--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 днрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\04,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C69B6-C2A6-466C-B8C5-0FFBDAFCE540}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A84B5A8-4C6B-4C44-9DF0-520A15433FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AN$134</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -806,7 +798,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -831,12 +823,10 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="12" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -858,7 +848,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -7449,14 +7439,13 @@
     <col min="22" max="23" width="7" customWidth="1"/>
     <col min="24" max="24" width="5.85546875" customWidth="1"/>
     <col min="25" max="27" width="7" customWidth="1"/>
-    <col min="28" max="28" width="21.85546875" style="25" customWidth="1"/>
+    <col min="28" max="28" width="4.42578125" style="24" customWidth="1"/>
     <col min="29" max="30" width="5" customWidth="1"/>
-    <col min="31" max="31" width="6.7109375" customWidth="1"/>
-    <col min="32" max="37" width="6.7109375" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="6.7109375" customWidth="1"/>
-    <col min="39" max="39" width="41.42578125" customWidth="1"/>
+    <col min="31" max="38" width="6.7109375" customWidth="1"/>
+    <col min="39" max="39" width="33.42578125" customWidth="1"/>
     <col min="40" max="40" width="7" customWidth="1"/>
-    <col min="41" max="47" width="3" customWidth="1"/>
+    <col min="41" max="41" width="6.7109375" customWidth="1"/>
+    <col min="42" max="47" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
@@ -7486,7 +7475,7 @@
       <c r="X1" s="16"/>
       <c r="Y1" s="16"/>
       <c r="Z1" s="16"/>
-      <c r="AA1" s="30">
+      <c r="AA1" s="28">
         <v>1.9</v>
       </c>
       <c r="AB1" s="16"/>
@@ -7982,7 +7971,7 @@
         <f>Z6</f>
         <v>0</v>
       </c>
-      <c r="AB6" s="24"/>
+      <c r="AB6" s="16"/>
       <c r="AC6" s="16">
         <f>(F6+O6+P6+Q6+R6+S6+T6+U6+V6+W6+X6+AA6)/Y6</f>
         <v>11.509368851288702</v>
@@ -8020,7 +8009,10 @@
         <f>ROUND(G6*AA6,0)</f>
         <v>0</v>
       </c>
-      <c r="AO6" s="16"/>
+      <c r="AO6" s="16">
+        <f>(SUM(AE6:AL6)+Y6)/9</f>
+        <v>415.19784444444434</v>
+      </c>
       <c r="AP6" s="16"/>
       <c r="AQ6" s="16"/>
       <c r="AR6" s="16"/>
@@ -8093,10 +8085,10 @@
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4">
-        <f t="shared" ref="AA7:AA70" si="6">Z7</f>
-        <v>0</v>
-      </c>
-      <c r="AB7" s="24"/>
+        <f t="shared" ref="AA7:AA69" si="6">Z7</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="16"/>
       <c r="AC7" s="16">
         <f t="shared" ref="AC7:AC70" si="7">(F7+O7+P7+Q7+R7+S7+T7+U7+V7+W7+X7+AA7)/Y7</f>
         <v>15.011404105768158</v>
@@ -8134,7 +8126,10 @@
         <f t="shared" ref="AN7:AN70" si="8">ROUND(G7*AA7,0)</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="16"/>
+      <c r="AO7" s="16">
+        <f t="shared" ref="AO7:AO70" si="9">(SUM(AE7:AL7)+Y7)/9</f>
+        <v>182.01339999999999</v>
+      </c>
       <c r="AP7" s="16"/>
       <c r="AQ7" s="16"/>
       <c r="AR7" s="16"/>
@@ -8208,14 +8203,14 @@
         <v>613.56360000000006</v>
       </c>
       <c r="Z8" s="4">
-        <f t="shared" ref="Z8:Z13" si="9">11*Y8-X8-W8-V8-U8-T8-S8-R8-Q8-P8-O8-F8</f>
+        <f t="shared" ref="Z8:Z13" si="10">11*Y8-X8-W8-V8-U8-T8-S8-R8-Q8-P8-O8-F8</f>
         <v>234.60192000000168</v>
       </c>
-      <c r="AA8" s="31">
+      <c r="AA8" s="29">
         <f>Z8+$AA$1*Y8</f>
         <v>1400.3727600000018</v>
       </c>
-      <c r="AB8" s="24"/>
+      <c r="AB8" s="16"/>
       <c r="AC8" s="16">
         <f t="shared" si="7"/>
         <v>12.9</v>
@@ -8253,7 +8248,10 @@
         <f t="shared" si="8"/>
         <v>1400</v>
       </c>
-      <c r="AO8" s="16"/>
+      <c r="AO8" s="16">
+        <f t="shared" si="9"/>
+        <v>559.58484444444446</v>
+      </c>
       <c r="AP8" s="16"/>
       <c r="AQ8" s="16"/>
       <c r="AR8" s="16"/>
@@ -8325,7 +8323,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB9" s="24"/>
+      <c r="AB9" s="16"/>
       <c r="AC9" s="16">
         <f t="shared" si="7"/>
         <v>24.083333333333332</v>
@@ -8365,7 +8363,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO9" s="16"/>
+      <c r="AO9" s="16">
+        <f t="shared" si="9"/>
+        <v>0.8</v>
+      </c>
       <c r="AP9" s="16"/>
       <c r="AQ9" s="16"/>
       <c r="AR9" s="16"/>
@@ -8441,7 +8442,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB10" s="24"/>
+      <c r="AB10" s="16"/>
       <c r="AC10" s="16">
         <f t="shared" si="7"/>
         <v>14.851460176991148</v>
@@ -8481,7 +8482,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO10" s="16"/>
+      <c r="AO10" s="16">
+        <f t="shared" si="9"/>
+        <v>497.39355555555551</v>
+      </c>
       <c r="AP10" s="16"/>
       <c r="AQ10" s="16"/>
       <c r="AR10" s="16"/>
@@ -8556,7 +8560,7 @@
       <c r="AA11" s="4">
         <v>1000</v>
       </c>
-      <c r="AB11" s="24" t="str">
+      <c r="AB11" s="16" t="str">
         <f>VLOOKUP(A11,[1]Sheet!$A:$AA,27,0)</f>
         <v>1000 сеть МКД</v>
       </c>
@@ -8599,7 +8603,10 @@
         <f t="shared" si="8"/>
         <v>450</v>
       </c>
-      <c r="AO11" s="16"/>
+      <c r="AO11" s="16">
+        <f t="shared" si="9"/>
+        <v>607.1835111111111</v>
+      </c>
       <c r="AP11" s="16"/>
       <c r="AQ11" s="16"/>
       <c r="AR11" s="16"/>
@@ -8671,7 +8678,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="24"/>
+      <c r="AB12" s="16"/>
       <c r="AC12" s="16">
         <f t="shared" si="7"/>
         <v>16.504237288135592</v>
@@ -8709,7 +8716,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO12" s="16"/>
+      <c r="AO12" s="16">
+        <f t="shared" si="9"/>
+        <v>18.088888888888889</v>
+      </c>
       <c r="AP12" s="16"/>
       <c r="AQ12" s="16"/>
       <c r="AR12" s="16"/>
@@ -8777,14 +8787,14 @@
         <v>11.8</v>
       </c>
       <c r="Z13" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46.2</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="6"/>
         <v>46.2</v>
       </c>
-      <c r="AB13" s="24"/>
+      <c r="AB13" s="16"/>
       <c r="AC13" s="16">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -8822,7 +8832,10 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="AO13" s="16"/>
+      <c r="AO13" s="16">
+        <f t="shared" si="9"/>
+        <v>6.1111111111111107</v>
+      </c>
       <c r="AP13" s="16"/>
       <c r="AQ13" s="16"/>
       <c r="AR13" s="16"/>
@@ -8894,7 +8907,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="24"/>
+      <c r="AB14" s="16"/>
       <c r="AC14" s="16">
         <f t="shared" si="7"/>
         <v>16.828804347826093</v>
@@ -8932,7 +8945,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO14" s="16"/>
+      <c r="AO14" s="16">
+        <f t="shared" si="9"/>
+        <v>45.977777777777781</v>
+      </c>
       <c r="AP14" s="16"/>
       <c r="AQ14" s="16"/>
       <c r="AR14" s="16"/>
@@ -9002,7 +9018,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="24"/>
+      <c r="AB15" s="16"/>
       <c r="AC15" s="16">
         <f t="shared" si="7"/>
         <v>82.272727272727266</v>
@@ -9042,7 +9058,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="16"/>
+      <c r="AO15" s="16">
+        <f t="shared" si="9"/>
+        <v>0.95555555555555571</v>
+      </c>
       <c r="AP15" s="16"/>
       <c r="AQ15" s="16"/>
       <c r="AR15" s="16"/>
@@ -9116,11 +9135,11 @@
         <v>693.11580000000004</v>
       </c>
       <c r="Z16" s="4"/>
-      <c r="AA16" s="31">
-        <f t="shared" ref="AA16:AA17" si="10">Z16+$AA$1*Y16</f>
+      <c r="AA16" s="29">
+        <f t="shared" ref="AA16:AA17" si="11">Z16+$AA$1*Y16</f>
         <v>1316.92002</v>
       </c>
-      <c r="AB16" s="24"/>
+      <c r="AB16" s="16"/>
       <c r="AC16" s="16">
         <f t="shared" si="7"/>
         <v>13.059703521402916</v>
@@ -9158,7 +9177,10 @@
         <f t="shared" si="8"/>
         <v>1317</v>
       </c>
-      <c r="AO16" s="16"/>
+      <c r="AO16" s="16">
+        <f t="shared" si="9"/>
+        <v>680.67037777777784</v>
+      </c>
       <c r="AP16" s="16"/>
       <c r="AQ16" s="16"/>
       <c r="AR16" s="16"/>
@@ -9230,14 +9252,14 @@
         <v>530.1232</v>
       </c>
       <c r="Z17" s="4">
-        <f t="shared" ref="Z17" si="11">11*Y17-X17-W17-V17-U17-T17-S17-R17-Q17-P17-O17-F17</f>
+        <f t="shared" ref="Z17" si="12">11*Y17-X17-W17-V17-U17-T17-S17-R17-Q17-P17-O17-F17</f>
         <v>368.88317000000006</v>
       </c>
-      <c r="AA17" s="31">
-        <f t="shared" si="10"/>
+      <c r="AA17" s="29">
+        <f t="shared" si="11"/>
         <v>1376.11725</v>
       </c>
-      <c r="AB17" s="24"/>
+      <c r="AB17" s="16"/>
       <c r="AC17" s="16">
         <f t="shared" si="7"/>
         <v>12.9</v>
@@ -9275,7 +9297,10 @@
         <f t="shared" si="8"/>
         <v>1376</v>
       </c>
-      <c r="AO17" s="16"/>
+      <c r="AO17" s="16">
+        <f t="shared" si="9"/>
+        <v>602.27486666666664</v>
+      </c>
       <c r="AP17" s="16"/>
       <c r="AQ17" s="16"/>
       <c r="AR17" s="16"/>
@@ -9349,7 +9374,7 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AB18" s="24"/>
+      <c r="AB18" s="16"/>
       <c r="AC18" s="16">
         <f t="shared" si="7"/>
         <v>15.697961815381309</v>
@@ -9387,7 +9412,10 @@
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="AO18" s="16"/>
+      <c r="AO18" s="16">
+        <f t="shared" si="9"/>
+        <v>41.154488888888892</v>
+      </c>
       <c r="AP18" s="16"/>
       <c r="AQ18" s="16"/>
       <c r="AR18" s="16"/>
@@ -9453,7 +9481,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="24"/>
+      <c r="AB19" s="16"/>
       <c r="AC19" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -9491,7 +9519,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="16"/>
+      <c r="AO19" s="16">
+        <f t="shared" si="9"/>
+        <v>0.10995555555555556</v>
+      </c>
       <c r="AP19" s="16"/>
       <c r="AQ19" s="16"/>
       <c r="AR19" s="16"/>
@@ -9551,7 +9582,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="24"/>
+      <c r="AB20" s="16"/>
       <c r="AC20" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -9591,7 +9622,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO20" s="16"/>
+      <c r="AO20" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP20" s="16"/>
       <c r="AQ20" s="16"/>
       <c r="AR20" s="16"/>
@@ -9661,7 +9695,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB21" s="24"/>
+      <c r="AB21" s="16"/>
       <c r="AC21" s="16">
         <f t="shared" si="7"/>
         <v>36.925407925407924</v>
@@ -9701,7 +9735,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="16"/>
+      <c r="AO21" s="16">
+        <f t="shared" si="9"/>
+        <v>0.74302222222222225</v>
+      </c>
       <c r="AP21" s="16"/>
       <c r="AQ21" s="16"/>
       <c r="AR21" s="16"/>
@@ -9773,14 +9810,14 @@
         <v>859.37340000000006</v>
       </c>
       <c r="Z22" s="4">
-        <f t="shared" ref="Z22" si="12">11*Y22-X22-W22-V22-U22-T22-S22-R22-Q22-P22-O22-F22</f>
+        <f t="shared" ref="Z22" si="13">11*Y22-X22-W22-V22-U22-T22-S22-R22-Q22-P22-O22-F22</f>
         <v>1485.5195739999986</v>
       </c>
-      <c r="AA22" s="31">
+      <c r="AA22" s="29">
         <f>Z22+$AA$1*Y22</f>
         <v>3118.3290339999985</v>
       </c>
-      <c r="AB22" s="24"/>
+      <c r="AB22" s="16"/>
       <c r="AC22" s="16">
         <f t="shared" si="7"/>
         <v>12.9</v>
@@ -9818,7 +9855,10 @@
         <f t="shared" si="8"/>
         <v>3118</v>
       </c>
-      <c r="AO22" s="16"/>
+      <c r="AO22" s="16">
+        <f t="shared" si="9"/>
+        <v>807.42540000000008</v>
+      </c>
       <c r="AP22" s="16"/>
       <c r="AQ22" s="16"/>
       <c r="AR22" s="16"/>
@@ -9884,7 +9924,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="24"/>
+      <c r="AB23" s="16"/>
       <c r="AC23" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -9922,7 +9962,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO23" s="16"/>
+      <c r="AO23" s="16">
+        <f t="shared" si="9"/>
+        <v>0.33302222222222222</v>
+      </c>
       <c r="AP23" s="16"/>
       <c r="AQ23" s="16"/>
       <c r="AR23" s="16"/>
@@ -9998,7 +10041,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB24" s="24"/>
+      <c r="AB24" s="16"/>
       <c r="AC24" s="16">
         <f t="shared" si="7"/>
         <v>33.286444802975204</v>
@@ -10038,7 +10081,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO24" s="16"/>
+      <c r="AO24" s="16">
+        <f t="shared" si="9"/>
+        <v>83.516177777777784</v>
+      </c>
       <c r="AP24" s="16"/>
       <c r="AQ24" s="16"/>
       <c r="AR24" s="16"/>
@@ -10110,14 +10156,14 @@
         <v>248.37119999999999</v>
       </c>
       <c r="Z25" s="4">
-        <f t="shared" ref="Z25" si="13">11*Y25-X25-W25-V25-U25-T25-S25-R25-Q25-P25-O25-F25</f>
+        <f t="shared" ref="Z25" si="14">11*Y25-X25-W25-V25-U25-T25-S25-R25-Q25-P25-O25-F25</f>
         <v>108.52065600000023</v>
       </c>
-      <c r="AA25" s="31">
+      <c r="AA25" s="29">
         <f>Z25+$AA$1*Y25</f>
         <v>580.42593600000021</v>
       </c>
-      <c r="AB25" s="24"/>
+      <c r="AB25" s="16"/>
       <c r="AC25" s="16">
         <f t="shared" si="7"/>
         <v>12.9</v>
@@ -10155,7 +10201,10 @@
         <f t="shared" si="8"/>
         <v>580</v>
       </c>
-      <c r="AO25" s="16"/>
+      <c r="AO25" s="16">
+        <f t="shared" si="9"/>
+        <v>224.93371111111111</v>
+      </c>
       <c r="AP25" s="16"/>
       <c r="AQ25" s="16"/>
       <c r="AR25" s="16"/>
@@ -10215,7 +10264,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB26" s="24"/>
+      <c r="AB26" s="16"/>
       <c r="AC26" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -10255,7 +10304,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO26" s="16"/>
+      <c r="AO26" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP26" s="16"/>
       <c r="AQ26" s="16"/>
       <c r="AR26" s="16"/>
@@ -10327,14 +10379,14 @@
         <v>453.67960000000005</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" ref="Z27" si="14">11*Y27-X27-W27-V27-U27-T27-S27-R27-Q27-P27-O27-F27</f>
+        <f t="shared" ref="Z27" si="15">11*Y27-X27-W27-V27-U27-T27-S27-R27-Q27-P27-O27-F27</f>
         <v>887.3375280000007</v>
       </c>
-      <c r="AA27" s="31">
+      <c r="AA27" s="29">
         <f>Z27+$AA$1*Y27</f>
         <v>1749.3287680000008</v>
       </c>
-      <c r="AB27" s="24"/>
+      <c r="AB27" s="16"/>
       <c r="AC27" s="16">
         <f t="shared" si="7"/>
         <v>12.9</v>
@@ -10372,7 +10424,10 @@
         <f t="shared" si="8"/>
         <v>1749</v>
       </c>
-      <c r="AO27" s="16"/>
+      <c r="AO27" s="16">
+        <f t="shared" si="9"/>
+        <v>401.5872</v>
+      </c>
       <c r="AP27" s="16"/>
       <c r="AQ27" s="16"/>
       <c r="AR27" s="16"/>
@@ -10442,7 +10497,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="24"/>
+      <c r="AB28" s="16"/>
       <c r="AC28" s="16">
         <f t="shared" si="7"/>
         <v>65.346721436178314</v>
@@ -10480,7 +10535,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO28" s="16"/>
+      <c r="AO28" s="16">
+        <f t="shared" si="9"/>
+        <v>6.2980666666666671</v>
+      </c>
       <c r="AP28" s="16"/>
       <c r="AQ28" s="16"/>
       <c r="AR28" s="16"/>
@@ -10540,7 +10598,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="24"/>
+      <c r="AB29" s="16"/>
       <c r="AC29" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -10580,7 +10638,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO29" s="16"/>
+      <c r="AO29" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP29" s="16"/>
       <c r="AQ29" s="16"/>
       <c r="AR29" s="16"/>
@@ -10640,7 +10701,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="24"/>
+      <c r="AB30" s="16"/>
       <c r="AC30" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -10680,7 +10741,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO30" s="16"/>
+      <c r="AO30" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP30" s="16"/>
       <c r="AQ30" s="16"/>
       <c r="AR30" s="16"/>
@@ -10758,7 +10822,7 @@
         <f t="shared" si="6"/>
         <v>600</v>
       </c>
-      <c r="AB31" s="24"/>
+      <c r="AB31" s="16"/>
       <c r="AC31" s="16">
         <f t="shared" si="7"/>
         <v>3.3543612023961007</v>
@@ -10796,7 +10860,10 @@
         <f t="shared" si="8"/>
         <v>600</v>
       </c>
-      <c r="AO31" s="16"/>
+      <c r="AO31" s="16">
+        <f t="shared" si="9"/>
+        <v>376.6624888888889</v>
+      </c>
       <c r="AP31" s="16"/>
       <c r="AQ31" s="16"/>
       <c r="AR31" s="16"/>
@@ -10866,7 +10933,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB32" s="24"/>
+      <c r="AB32" s="16"/>
       <c r="AC32" s="16">
         <f t="shared" si="7"/>
         <v>2.3469387755102042</v>
@@ -10904,7 +10971,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO32" s="16"/>
+      <c r="AO32" s="16">
+        <f t="shared" si="9"/>
+        <v>7.5326222222222237</v>
+      </c>
       <c r="AP32" s="16"/>
       <c r="AQ32" s="16"/>
       <c r="AR32" s="16"/>
@@ -10982,7 +11052,7 @@
         <f t="shared" si="6"/>
         <v>800</v>
       </c>
-      <c r="AB33" s="24"/>
+      <c r="AB33" s="16"/>
       <c r="AC33" s="16">
         <f t="shared" si="7"/>
         <v>69.804172247250307</v>
@@ -11020,7 +11090,10 @@
         <f t="shared" si="8"/>
         <v>800</v>
       </c>
-      <c r="AO33" s="16"/>
+      <c r="AO33" s="16">
+        <f t="shared" si="9"/>
+        <v>1097.6750888888889</v>
+      </c>
       <c r="AP33" s="16"/>
       <c r="AQ33" s="16"/>
       <c r="AR33" s="16"/>
@@ -11080,7 +11153,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB34" s="24"/>
+      <c r="AB34" s="16"/>
       <c r="AC34" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -11120,7 +11193,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO34" s="16"/>
+      <c r="AO34" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP34" s="16"/>
       <c r="AQ34" s="16"/>
       <c r="AR34" s="16"/>
@@ -11180,7 +11256,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="24"/>
+      <c r="AB35" s="16"/>
       <c r="AC35" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -11220,7 +11296,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO35" s="16"/>
+      <c r="AO35" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP35" s="16"/>
       <c r="AQ35" s="16"/>
       <c r="AR35" s="16"/>
@@ -11280,7 +11359,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="24"/>
+      <c r="AB36" s="16"/>
       <c r="AC36" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -11320,7 +11399,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO36" s="16"/>
+      <c r="AO36" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP36" s="16"/>
       <c r="AQ36" s="16"/>
       <c r="AR36" s="16"/>
@@ -11380,7 +11462,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="24"/>
+      <c r="AB37" s="16"/>
       <c r="AC37" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -11420,7 +11502,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO37" s="16"/>
+      <c r="AO37" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP37" s="16"/>
       <c r="AQ37" s="16"/>
       <c r="AR37" s="16"/>
@@ -11461,11 +11546,11 @@
         <v>4389</v>
       </c>
       <c r="L38" s="16">
-        <f t="shared" ref="L38:L69" si="15">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="16">E38-K38</f>
         <v>-333</v>
       </c>
       <c r="M38" s="8">
-        <f t="shared" ref="M38:M69" si="16">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="17">E38-N38</f>
         <v>4056</v>
       </c>
       <c r="N38" s="16"/>
@@ -11490,7 +11575,7 @@
       </c>
       <c r="X38" s="16"/>
       <c r="Y38" s="16">
-        <f t="shared" ref="Y38:Y69" si="17">M38/5</f>
+        <f t="shared" ref="Y38:Y69" si="18">M38/5</f>
         <v>811.2</v>
       </c>
       <c r="Z38" s="22">
@@ -11500,13 +11585,13 @@
         <f t="shared" si="6"/>
         <v>800</v>
       </c>
-      <c r="AB38" s="24"/>
+      <c r="AB38" s="16"/>
       <c r="AC38" s="16">
         <f t="shared" si="7"/>
         <v>4.162498461538461</v>
       </c>
       <c r="AD38" s="16">
-        <f t="shared" ref="AD38:AD69" si="18">(F38+O38+P38+Q38+R38+S38+T38+U38+V38+W38+X38)/Y38</f>
+        <f t="shared" ref="AD38:AD69" si="19">(F38+O38+P38+Q38+R38+S38+T38+U38+V38+W38+X38)/Y38</f>
         <v>3.1763051676528598</v>
       </c>
       <c r="AE38" s="16">
@@ -11538,7 +11623,10 @@
         <f t="shared" si="8"/>
         <v>320</v>
       </c>
-      <c r="AO38" s="16"/>
+      <c r="AO38" s="16">
+        <f t="shared" si="9"/>
+        <v>775.06666666666661</v>
+      </c>
       <c r="AP38" s="16"/>
       <c r="AQ38" s="16"/>
       <c r="AR38" s="16"/>
@@ -11579,11 +11667,11 @@
         <v>619</v>
       </c>
       <c r="L39" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-127</v>
       </c>
       <c r="M39" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>492</v>
       </c>
       <c r="N39" s="16"/>
@@ -11602,7 +11690,7 @@
       <c r="W39" s="16"/>
       <c r="X39" s="16"/>
       <c r="Y39" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>98.4</v>
       </c>
       <c r="Z39" s="4"/>
@@ -11610,13 +11698,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB39" s="24"/>
+      <c r="AB39" s="16"/>
       <c r="AC39" s="16">
         <f t="shared" si="7"/>
         <v>15.266544715447154</v>
       </c>
       <c r="AD39" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.266544715447154</v>
       </c>
       <c r="AE39" s="16">
@@ -11648,7 +11736,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO39" s="16"/>
+      <c r="AO39" s="16">
+        <f t="shared" si="9"/>
+        <v>134.44444444444446</v>
+      </c>
       <c r="AP39" s="16"/>
       <c r="AQ39" s="16"/>
       <c r="AR39" s="16"/>
@@ -11689,11 +11780,11 @@
         <v>1281</v>
       </c>
       <c r="L40" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-447</v>
       </c>
       <c r="M40" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>834</v>
       </c>
       <c r="N40" s="16"/>
@@ -11714,7 +11805,7 @@
       <c r="W40" s="16"/>
       <c r="X40" s="16"/>
       <c r="Y40" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>166.8</v>
       </c>
       <c r="Z40" s="22">
@@ -11724,13 +11815,13 @@
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
-      <c r="AB40" s="24"/>
+      <c r="AB40" s="16"/>
       <c r="AC40" s="16">
         <f t="shared" si="7"/>
         <v>4.3405275779376495</v>
       </c>
       <c r="AD40" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.5419664268585129</v>
       </c>
       <c r="AE40" s="16">
@@ -11762,7 +11853,10 @@
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="AO40" s="16"/>
+      <c r="AO40" s="16">
+        <f t="shared" si="9"/>
+        <v>198.93333333333334</v>
+      </c>
       <c r="AP40" s="16"/>
       <c r="AQ40" s="16"/>
       <c r="AR40" s="16"/>
@@ -11803,11 +11897,11 @@
         <v>907</v>
       </c>
       <c r="L41" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-326</v>
       </c>
       <c r="M41" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>581</v>
       </c>
       <c r="N41" s="16"/>
@@ -11828,7 +11922,7 @@
       <c r="W41" s="16"/>
       <c r="X41" s="16"/>
       <c r="Y41" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>116.2</v>
       </c>
       <c r="Z41" s="22">
@@ -11838,13 +11932,13 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
-      <c r="AB41" s="24"/>
+      <c r="AB41" s="16"/>
       <c r="AC41" s="16">
         <f t="shared" si="7"/>
         <v>4.4590361445783131</v>
       </c>
       <c r="AD41" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.737865748709122</v>
       </c>
       <c r="AE41" s="16">
@@ -11876,7 +11970,10 @@
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
-      <c r="AO41" s="16"/>
+      <c r="AO41" s="16">
+        <f t="shared" si="9"/>
+        <v>96.022222222222226</v>
+      </c>
       <c r="AP41" s="16"/>
       <c r="AQ41" s="16"/>
       <c r="AR41" s="16"/>
@@ -11905,11 +12002,11 @@
       <c r="J42" s="16"/>
       <c r="K42" s="16"/>
       <c r="L42" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M42" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N42" s="16"/>
@@ -11928,22 +12025,22 @@
       <c r="W42" s="16"/>
       <c r="X42" s="16"/>
       <c r="Y42" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z42" s="4">
         <v>50</v>
       </c>
-      <c r="AA42" s="27">
+      <c r="AA42" s="26">
         <v>300</v>
       </c>
-      <c r="AB42" s="24"/>
+      <c r="AB42" s="16"/>
       <c r="AC42" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD42" s="16" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE42" s="16">
@@ -11970,14 +12067,17 @@
       <c r="AL42" s="16">
         <v>0</v>
       </c>
-      <c r="AM42" s="29" t="s">
+      <c r="AM42" s="27" t="s">
         <v>191</v>
       </c>
       <c r="AN42" s="16">
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="AO42" s="16"/>
+      <c r="AO42" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP42" s="16"/>
       <c r="AQ42" s="16"/>
       <c r="AR42" s="16"/>
@@ -12018,11 +12118,11 @@
         <v>211</v>
       </c>
       <c r="L43" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-24</v>
       </c>
       <c r="M43" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>187</v>
       </c>
       <c r="N43" s="16"/>
@@ -12043,7 +12143,7 @@
       <c r="W43" s="16"/>
       <c r="X43" s="16"/>
       <c r="Y43" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>37.4</v>
       </c>
       <c r="Z43" s="4"/>
@@ -12051,13 +12151,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB43" s="24"/>
+      <c r="AB43" s="16"/>
       <c r="AC43" s="16">
         <f t="shared" si="7"/>
         <v>15.724598930481285</v>
       </c>
       <c r="AD43" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.724598930481285</v>
       </c>
       <c r="AE43" s="16">
@@ -12089,7 +12189,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO43" s="16"/>
+      <c r="AO43" s="16">
+        <f t="shared" si="9"/>
+        <v>44.511111111111106</v>
+      </c>
       <c r="AP43" s="16"/>
       <c r="AQ43" s="16"/>
       <c r="AR43" s="16"/>
@@ -12130,11 +12233,11 @@
         <v>113</v>
       </c>
       <c r="L44" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-19</v>
       </c>
       <c r="M44" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>94</v>
       </c>
       <c r="N44" s="16"/>
@@ -12153,24 +12256,24 @@
       <c r="W44" s="16"/>
       <c r="X44" s="16"/>
       <c r="Y44" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>18.8</v>
       </c>
       <c r="Z44" s="4">
-        <f t="shared" ref="Z44:Z52" si="19">11*Y44-X44-W44-V44-U44-T44-S44-R44-Q44-P44-O44-F44</f>
+        <f t="shared" ref="Z44:Z52" si="20">11*Y44-X44-W44-V44-U44-T44-S44-R44-Q44-P44-O44-F44</f>
         <v>81.800000000000011</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="6"/>
         <v>81.800000000000011</v>
       </c>
-      <c r="AB44" s="24"/>
+      <c r="AB44" s="16"/>
       <c r="AC44" s="16">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AD44" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.6489361702127656</v>
       </c>
       <c r="AE44" s="16">
@@ -12202,7 +12305,10 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="AO44" s="16"/>
+      <c r="AO44" s="16">
+        <f t="shared" si="9"/>
+        <v>17.333333333333332</v>
+      </c>
       <c r="AP44" s="16"/>
       <c r="AQ44" s="16"/>
       <c r="AR44" s="16"/>
@@ -12243,11 +12349,11 @@
         <v>20.6</v>
       </c>
       <c r="L45" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-4.0680000000000014</v>
       </c>
       <c r="M45" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>16.532</v>
       </c>
       <c r="N45" s="16"/>
@@ -12266,24 +12372,24 @@
       <c r="W45" s="16"/>
       <c r="X45" s="16"/>
       <c r="Y45" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.3064</v>
       </c>
       <c r="Z45" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.0674000000000028</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="6"/>
         <v>9.0674000000000028</v>
       </c>
-      <c r="AB45" s="24"/>
+      <c r="AB45" s="16"/>
       <c r="AC45" s="16">
         <f t="shared" si="7"/>
         <v>11.000000000000002</v>
       </c>
       <c r="AD45" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8.257621582385676</v>
       </c>
       <c r="AE45" s="16">
@@ -12315,7 +12421,10 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="AO45" s="16"/>
+      <c r="AO45" s="16">
+        <f t="shared" si="9"/>
+        <v>2.6902222222222223</v>
+      </c>
       <c r="AP45" s="16"/>
       <c r="AQ45" s="16"/>
       <c r="AR45" s="16"/>
@@ -12354,11 +12463,11 @@
         <v>268</v>
       </c>
       <c r="L46" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-272</v>
       </c>
       <c r="M46" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="N46" s="16"/>
@@ -12377,24 +12486,24 @@
       <c r="W46" s="16"/>
       <c r="X46" s="16"/>
       <c r="Y46" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.8</v>
       </c>
       <c r="Z46" s="22">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>20.2</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="6"/>
         <v>20.2</v>
       </c>
-      <c r="AB46" s="24"/>
+      <c r="AB46" s="16"/>
       <c r="AC46" s="16">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AD46" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>36.25</v>
       </c>
       <c r="AE46" s="16">
@@ -12426,7 +12535,10 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="AO46" s="16"/>
+      <c r="AO46" s="16">
+        <f t="shared" si="9"/>
+        <v>1.0222222222222221</v>
+      </c>
       <c r="AP46" s="16"/>
       <c r="AQ46" s="16"/>
       <c r="AR46" s="16"/>
@@ -12467,11 +12579,11 @@
         <v>321</v>
       </c>
       <c r="L47" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-191</v>
       </c>
       <c r="M47" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>130</v>
       </c>
       <c r="N47" s="16"/>
@@ -12492,7 +12604,7 @@
       <c r="W47" s="16"/>
       <c r="X47" s="16"/>
       <c r="Y47" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="Z47" s="22">
@@ -12502,13 +12614,13 @@
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="AB47" s="24"/>
+      <c r="AB47" s="16"/>
       <c r="AC47" s="16">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="AD47" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="AE47" s="16">
@@ -12540,7 +12652,10 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="AO47" s="16"/>
+      <c r="AO47" s="16">
+        <f t="shared" si="9"/>
+        <v>45.55555555555555</v>
+      </c>
       <c r="AP47" s="16"/>
       <c r="AQ47" s="16"/>
       <c r="AR47" s="16"/>
@@ -12581,11 +12696,11 @@
         <v>49.5</v>
       </c>
       <c r="L48" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-40.393999999999998</v>
       </c>
       <c r="M48" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.1059999999999999</v>
       </c>
       <c r="N48" s="16"/>
@@ -12604,7 +12719,7 @@
       <c r="W48" s="16"/>
       <c r="X48" s="16"/>
       <c r="Y48" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.8211999999999999</v>
       </c>
       <c r="Z48" s="4"/>
@@ -12612,13 +12727,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB48" s="24"/>
+      <c r="AB48" s="16"/>
       <c r="AC48" s="16">
         <f t="shared" si="7"/>
         <v>43.29875905996046</v>
       </c>
       <c r="AD48" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>43.29875905996046</v>
       </c>
       <c r="AE48" s="16">
@@ -12652,7 +12767,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO48" s="16"/>
+      <c r="AO48" s="16">
+        <f t="shared" si="9"/>
+        <v>5.0491777777777767</v>
+      </c>
       <c r="AP48" s="16"/>
       <c r="AQ48" s="16"/>
       <c r="AR48" s="16"/>
@@ -12693,11 +12811,11 @@
         <v>495</v>
       </c>
       <c r="L49" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-31</v>
       </c>
       <c r="M49" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>464</v>
       </c>
       <c r="N49" s="16"/>
@@ -12720,7 +12838,7 @@
       </c>
       <c r="X49" s="16"/>
       <c r="Y49" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>92.8</v>
       </c>
       <c r="Z49" s="4"/>
@@ -12728,13 +12846,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB49" s="24"/>
+      <c r="AB49" s="16"/>
       <c r="AC49" s="16">
         <f t="shared" si="7"/>
         <v>12.923491379310345</v>
       </c>
       <c r="AD49" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.923491379310345</v>
       </c>
       <c r="AE49" s="16">
@@ -12768,7 +12886,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO49" s="16"/>
+      <c r="AO49" s="16">
+        <f t="shared" si="9"/>
+        <v>137.13333333333333</v>
+      </c>
       <c r="AP49" s="16"/>
       <c r="AQ49" s="16"/>
       <c r="AR49" s="16"/>
@@ -12809,11 +12930,11 @@
         <v>566</v>
       </c>
       <c r="L50" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-323</v>
       </c>
       <c r="M50" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>243</v>
       </c>
       <c r="N50" s="16"/>
@@ -12836,7 +12957,7 @@
       </c>
       <c r="X50" s="16"/>
       <c r="Y50" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>48.6</v>
       </c>
       <c r="Z50" s="4"/>
@@ -12844,13 +12965,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB50" s="24"/>
+      <c r="AB50" s="16"/>
       <c r="AC50" s="16">
         <f t="shared" si="7"/>
         <v>13.165152263374484</v>
       </c>
       <c r="AD50" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.165152263374484</v>
       </c>
       <c r="AE50" s="16">
@@ -12882,7 +13003,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO50" s="16"/>
+      <c r="AO50" s="16">
+        <f t="shared" si="9"/>
+        <v>58.555555555555557</v>
+      </c>
       <c r="AP50" s="16"/>
       <c r="AQ50" s="16"/>
       <c r="AR50" s="16"/>
@@ -12923,11 +13047,11 @@
         <v>108.4</v>
       </c>
       <c r="L51" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-24.38900000000001</v>
       </c>
       <c r="M51" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84.010999999999996</v>
       </c>
       <c r="N51" s="16"/>
@@ -12946,24 +13070,24 @@
       <c r="W51" s="16"/>
       <c r="X51" s="16"/>
       <c r="Y51" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>16.802199999999999</v>
       </c>
       <c r="Z51" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>52.131800000000041</v>
       </c>
       <c r="AA51" s="4">
         <f t="shared" si="6"/>
         <v>52.131800000000041</v>
       </c>
-      <c r="AB51" s="24"/>
+      <c r="AB51" s="16"/>
       <c r="AC51" s="16">
         <f t="shared" si="7"/>
         <v>11.000000000000002</v>
       </c>
       <c r="AD51" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.8973229696111202</v>
       </c>
       <c r="AE51" s="16">
@@ -12995,7 +13119,10 @@
         <f t="shared" si="8"/>
         <v>52</v>
       </c>
-      <c r="AO51" s="16"/>
+      <c r="AO51" s="16">
+        <f t="shared" si="9"/>
+        <v>17.708466666666666</v>
+      </c>
       <c r="AP51" s="16"/>
       <c r="AQ51" s="16"/>
       <c r="AR51" s="16"/>
@@ -13036,11 +13163,11 @@
         <v>578.75</v>
       </c>
       <c r="L52" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-35.647000000000048</v>
       </c>
       <c r="M52" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>543.10299999999995</v>
       </c>
       <c r="N52" s="16"/>
@@ -13059,24 +13186,24 @@
       <c r="W52" s="16"/>
       <c r="X52" s="16"/>
       <c r="Y52" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>108.6206</v>
       </c>
       <c r="Z52" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>501.82369999999986</v>
       </c>
-      <c r="AA52" s="31">
+      <c r="AA52" s="29">
         <f>Z52+$AA$1*Y52</f>
         <v>708.20283999999981</v>
       </c>
-      <c r="AB52" s="24"/>
+      <c r="AB52" s="16"/>
       <c r="AC52" s="16">
         <f t="shared" si="7"/>
         <v>12.899999999999999</v>
       </c>
       <c r="AD52" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.3800319644708274</v>
       </c>
       <c r="AE52" s="16">
@@ -13108,7 +13235,10 @@
         <f t="shared" si="8"/>
         <v>708</v>
       </c>
-      <c r="AO52" s="16"/>
+      <c r="AO52" s="16">
+        <f t="shared" si="9"/>
+        <v>80.772311111111108</v>
+      </c>
       <c r="AP52" s="16"/>
       <c r="AQ52" s="16"/>
       <c r="AR52" s="16"/>
@@ -13137,11 +13267,11 @@
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M53" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N53" s="10"/>
@@ -13160,7 +13290,7 @@
       <c r="W53" s="10"/>
       <c r="X53" s="10"/>
       <c r="Y53" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z53" s="12"/>
@@ -13168,13 +13298,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB53" s="24"/>
+      <c r="AB53" s="16"/>
       <c r="AC53" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD53" s="10" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE53" s="10">
@@ -13208,7 +13338,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO53" s="16"/>
+      <c r="AO53" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP53" s="16"/>
       <c r="AQ53" s="16"/>
       <c r="AR53" s="16"/>
@@ -13249,11 +13382,11 @@
         <v>435</v>
       </c>
       <c r="L54" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-38</v>
       </c>
       <c r="M54" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>397</v>
       </c>
       <c r="N54" s="16"/>
@@ -13274,7 +13407,7 @@
       <c r="W54" s="16"/>
       <c r="X54" s="16"/>
       <c r="Y54" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>79.400000000000006</v>
       </c>
       <c r="Z54" s="4"/>
@@ -13282,13 +13415,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB54" s="24"/>
+      <c r="AB54" s="16"/>
       <c r="AC54" s="16">
         <f t="shared" si="7"/>
         <v>11.137279596977329</v>
       </c>
       <c r="AD54" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.137279596977329</v>
       </c>
       <c r="AE54" s="16">
@@ -13320,7 +13453,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO54" s="16"/>
+      <c r="AO54" s="16">
+        <f t="shared" si="9"/>
+        <v>82.8</v>
+      </c>
       <c r="AP54" s="16"/>
       <c r="AQ54" s="16"/>
       <c r="AR54" s="16"/>
@@ -13361,11 +13497,11 @@
         <v>497</v>
       </c>
       <c r="L55" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-67</v>
       </c>
       <c r="M55" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>430</v>
       </c>
       <c r="N55" s="16"/>
@@ -13386,7 +13522,7 @@
       <c r="W55" s="16"/>
       <c r="X55" s="16"/>
       <c r="Y55" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>86</v>
       </c>
       <c r="Z55" s="4"/>
@@ -13394,13 +13530,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB55" s="24"/>
+      <c r="AB55" s="16"/>
       <c r="AC55" s="16">
         <f t="shared" si="7"/>
         <v>14.697674418604651</v>
       </c>
       <c r="AD55" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>14.697674418604651</v>
       </c>
       <c r="AE55" s="16">
@@ -13432,7 +13568,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO55" s="16"/>
+      <c r="AO55" s="16">
+        <f t="shared" si="9"/>
+        <v>111.13333333333334</v>
+      </c>
       <c r="AP55" s="16"/>
       <c r="AQ55" s="16"/>
       <c r="AR55" s="16"/>
@@ -13461,11 +13600,11 @@
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M56" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N56" s="10"/>
@@ -13484,7 +13623,7 @@
       <c r="W56" s="10"/>
       <c r="X56" s="10"/>
       <c r="Y56" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z56" s="12"/>
@@ -13492,13 +13631,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB56" s="24"/>
+      <c r="AB56" s="16"/>
       <c r="AC56" s="16" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD56" s="10" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE56" s="10">
@@ -13532,7 +13671,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO56" s="16"/>
+      <c r="AO56" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AP56" s="16"/>
       <c r="AQ56" s="16"/>
       <c r="AR56" s="16"/>
@@ -13573,11 +13715,11 @@
         <v>28</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-14</v>
       </c>
       <c r="M57" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="N57" s="16"/>
@@ -13596,7 +13738,7 @@
       <c r="W57" s="16"/>
       <c r="X57" s="16"/>
       <c r="Y57" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.8</v>
       </c>
       <c r="Z57" s="4"/>
@@ -13604,13 +13746,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB57" s="24"/>
+      <c r="AB57" s="16"/>
       <c r="AC57" s="16">
         <f t="shared" si="7"/>
         <v>13.578571428571431</v>
       </c>
       <c r="AD57" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.578571428571431</v>
       </c>
       <c r="AE57" s="16">
@@ -13642,7 +13784,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO57" s="16"/>
+      <c r="AO57" s="16">
+        <f t="shared" si="9"/>
+        <v>3.0222222222222221</v>
+      </c>
       <c r="AP57" s="16"/>
       <c r="AQ57" s="16"/>
       <c r="AR57" s="16"/>
@@ -13683,11 +13828,11 @@
         <v>357.85</v>
       </c>
       <c r="L58" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-13.645000000000039</v>
       </c>
       <c r="M58" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>344.20499999999998</v>
       </c>
       <c r="N58" s="16"/>
@@ -13706,7 +13851,7 @@
       <c r="W58" s="16"/>
       <c r="X58" s="16"/>
       <c r="Y58" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>68.840999999999994</v>
       </c>
       <c r="Z58" s="4"/>
@@ -13714,13 +13859,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB58" s="24"/>
+      <c r="AB58" s="16"/>
       <c r="AC58" s="16">
         <f t="shared" si="7"/>
         <v>11.210536395462009</v>
       </c>
       <c r="AD58" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.210536395462009</v>
       </c>
       <c r="AE58" s="16">
@@ -13752,7 +13897,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO58" s="16"/>
+      <c r="AO58" s="16">
+        <f t="shared" si="9"/>
+        <v>93.102000000000004</v>
+      </c>
       <c r="AP58" s="16"/>
       <c r="AQ58" s="16"/>
       <c r="AR58" s="16"/>
@@ -13793,11 +13941,11 @@
         <v>123</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M59" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>122</v>
       </c>
       <c r="N59" s="16"/>
@@ -13816,24 +13964,24 @@
       <c r="W59" s="16"/>
       <c r="X59" s="16"/>
       <c r="Y59" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>24.4</v>
       </c>
       <c r="Z59" s="4">
-        <f t="shared" ref="Z59:Z70" si="20">11*Y59-X59-W59-V59-U59-T59-S59-R59-Q59-P59-O59-F59</f>
+        <f t="shared" ref="Z59:Z70" si="21">11*Y59-X59-W59-V59-U59-T59-S59-R59-Q59-P59-O59-F59</f>
         <v>17.800000000000011</v>
       </c>
       <c r="AA59" s="4">
         <f t="shared" si="6"/>
         <v>17.800000000000011</v>
       </c>
-      <c r="AB59" s="24"/>
+      <c r="AB59" s="16"/>
       <c r="AC59" s="16">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AD59" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.270491803278688</v>
       </c>
       <c r="AE59" s="16">
@@ -13865,7 +14013,10 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AO59" s="16"/>
+      <c r="AO59" s="16">
+        <f t="shared" si="9"/>
+        <v>24.733333333333334</v>
+      </c>
       <c r="AP59" s="16"/>
       <c r="AQ59" s="16"/>
       <c r="AR59" s="16"/>
@@ -13906,11 +14057,11 @@
         <v>760.72299999999996</v>
       </c>
       <c r="L60" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-364.42199999999997</v>
       </c>
       <c r="M60" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>288.97800000000001</v>
       </c>
       <c r="N60" s="16">
@@ -13931,7 +14082,7 @@
       <c r="W60" s="16"/>
       <c r="X60" s="16"/>
       <c r="Y60" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>57.7956</v>
       </c>
       <c r="Z60" s="4"/>
@@ -13939,13 +14090,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB60" s="24"/>
+      <c r="AB60" s="16"/>
       <c r="AC60" s="16">
         <f t="shared" si="7"/>
         <v>15.748728276893047</v>
       </c>
       <c r="AD60" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.748728276893047</v>
       </c>
       <c r="AE60" s="16">
@@ -13977,7 +14128,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO60" s="16"/>
+      <c r="AO60" s="16">
+        <f t="shared" si="9"/>
+        <v>80.020377777777782</v>
+      </c>
       <c r="AP60" s="16"/>
       <c r="AQ60" s="16"/>
       <c r="AR60" s="16"/>
@@ -14016,11 +14170,11 @@
         <v>19.600000000000001</v>
       </c>
       <c r="L61" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.69900000000000162</v>
       </c>
       <c r="M61" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>18.901</v>
       </c>
       <c r="N61" s="16"/>
@@ -14039,7 +14193,7 @@
       <c r="W61" s="16"/>
       <c r="X61" s="16"/>
       <c r="Y61" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.7801999999999998</v>
       </c>
       <c r="Z61" s="4"/>
@@ -14047,13 +14201,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB61" s="24"/>
+      <c r="AB61" s="16"/>
       <c r="AC61" s="16">
         <f t="shared" si="7"/>
         <v>21.606264218824403</v>
       </c>
       <c r="AD61" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>21.606264218824403</v>
       </c>
       <c r="AE61" s="16">
@@ -14085,7 +14239,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO61" s="16"/>
+      <c r="AO61" s="16">
+        <f t="shared" si="9"/>
+        <v>5.0143777777777778</v>
+      </c>
       <c r="AP61" s="16"/>
       <c r="AQ61" s="16"/>
       <c r="AR61" s="16"/>
@@ -14126,11 +14283,11 @@
         <v>119</v>
       </c>
       <c r="L62" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M62" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>118</v>
       </c>
       <c r="N62" s="16"/>
@@ -14149,24 +14306,24 @@
       <c r="W62" s="16"/>
       <c r="X62" s="16"/>
       <c r="Y62" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>23.6</v>
       </c>
       <c r="Z62" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>50.100000000000009</v>
       </c>
       <c r="AA62" s="4">
         <f t="shared" si="6"/>
         <v>50.100000000000009</v>
       </c>
-      <c r="AB62" s="24"/>
+      <c r="AB62" s="16"/>
       <c r="AC62" s="16">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AD62" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8.8771186440677958</v>
       </c>
       <c r="AE62" s="16">
@@ -14198,7 +14355,10 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="AO62" s="16"/>
+      <c r="AO62" s="16">
+        <f t="shared" si="9"/>
+        <v>23.111111111111111</v>
+      </c>
       <c r="AP62" s="16"/>
       <c r="AQ62" s="16"/>
       <c r="AR62" s="16"/>
@@ -14239,11 +14399,11 @@
         <v>12</v>
       </c>
       <c r="L63" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M63" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="N63" s="16"/>
@@ -14262,7 +14422,7 @@
       <c r="W63" s="16"/>
       <c r="X63" s="16"/>
       <c r="Y63" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="Z63" s="4"/>
@@ -14270,13 +14430,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB63" s="24"/>
+      <c r="AB63" s="16"/>
       <c r="AC63" s="16">
         <f t="shared" si="7"/>
         <v>11.363636363636363</v>
       </c>
       <c r="AD63" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.363636363636363</v>
       </c>
       <c r="AE63" s="16">
@@ -14308,7 +14468,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO63" s="16"/>
+      <c r="AO63" s="16">
+        <f t="shared" si="9"/>
+        <v>1.622222222222222</v>
+      </c>
       <c r="AP63" s="16"/>
       <c r="AQ63" s="16"/>
       <c r="AR63" s="16"/>
@@ -14347,11 +14510,11 @@
         <v>64.900000000000006</v>
       </c>
       <c r="L64" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.55100000000000193</v>
       </c>
       <c r="M64" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>64.349000000000004</v>
       </c>
       <c r="N64" s="16"/>
@@ -14370,20 +14533,20 @@
       <c r="W64" s="16"/>
       <c r="X64" s="16"/>
       <c r="Y64" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>12.869800000000001</v>
       </c>
       <c r="Z64" s="4"/>
-      <c r="AA64" s="27">
+      <c r="AA64" s="26">
         <v>300</v>
       </c>
-      <c r="AB64" s="24"/>
+      <c r="AB64" s="16"/>
       <c r="AC64" s="16">
         <f t="shared" si="7"/>
         <v>34.873502307728167</v>
       </c>
       <c r="AD64" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.563116753951109</v>
       </c>
       <c r="AE64" s="16">
@@ -14410,14 +14573,17 @@
       <c r="AL64" s="16">
         <v>12.6326</v>
       </c>
-      <c r="AM64" s="28" t="s">
+      <c r="AM64" s="27" t="s">
         <v>190</v>
       </c>
       <c r="AN64" s="16">
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="AO64" s="16"/>
+      <c r="AO64" s="16">
+        <f t="shared" si="9"/>
+        <v>10.868822222222223</v>
+      </c>
       <c r="AP64" s="16"/>
       <c r="AQ64" s="16"/>
       <c r="AR64" s="16"/>
@@ -14458,11 +14624,11 @@
         <v>90.3</v>
       </c>
       <c r="L65" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-88.956000000000003</v>
       </c>
       <c r="M65" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.3440000000000001</v>
       </c>
       <c r="N65" s="16"/>
@@ -14481,20 +14647,20 @@
       <c r="W65" s="16"/>
       <c r="X65" s="16"/>
       <c r="Y65" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.26880000000000004</v>
       </c>
       <c r="Z65" s="4"/>
-      <c r="AA65" s="27">
+      <c r="AA65" s="26">
         <v>300</v>
       </c>
-      <c r="AB65" s="24"/>
+      <c r="AB65" s="16"/>
       <c r="AC65" s="16">
         <f t="shared" si="7"/>
         <v>1788.7470238095236</v>
       </c>
       <c r="AD65" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>672.67559523809507</v>
       </c>
       <c r="AE65" s="16">
@@ -14521,14 +14687,17 @@
       <c r="AL65" s="16">
         <v>0.30680000000000002</v>
       </c>
-      <c r="AM65" s="28" t="s">
+      <c r="AM65" s="27" t="s">
         <v>190</v>
       </c>
       <c r="AN65" s="16">
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="AO65" s="16"/>
+      <c r="AO65" s="16">
+        <f t="shared" si="9"/>
+        <v>2.5757333333333334</v>
+      </c>
       <c r="AP65" s="16"/>
       <c r="AQ65" s="16"/>
       <c r="AR65" s="16"/>
@@ -14569,11 +14738,11 @@
         <v>519</v>
       </c>
       <c r="L66" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-71</v>
       </c>
       <c r="M66" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>448</v>
       </c>
       <c r="N66" s="16"/>
@@ -14592,24 +14761,24 @@
       <c r="W66" s="16"/>
       <c r="X66" s="16"/>
       <c r="Y66" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>89.6</v>
       </c>
       <c r="Z66" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>392.13199999999995</v>
       </c>
-      <c r="AA66" s="31">
+      <c r="AA66" s="29">
         <f>Z66+$AA$1*Y66</f>
         <v>562.37199999999996</v>
       </c>
-      <c r="AB66" s="24"/>
+      <c r="AB66" s="16"/>
       <c r="AC66" s="16">
         <f t="shared" si="7"/>
         <v>12.9</v>
       </c>
       <c r="AD66" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.6235267857142857</v>
       </c>
       <c r="AE66" s="16">
@@ -14641,7 +14810,10 @@
         <f t="shared" si="8"/>
         <v>225</v>
       </c>
-      <c r="AO66" s="16"/>
+      <c r="AO66" s="16">
+        <f t="shared" si="9"/>
+        <v>100.84444444444445</v>
+      </c>
       <c r="AP66" s="16"/>
       <c r="AQ66" s="16"/>
       <c r="AR66" s="16"/>
@@ -14682,11 +14854,11 @@
         <v>41</v>
       </c>
       <c r="L67" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-37</v>
       </c>
       <c r="M67" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="N67" s="16"/>
@@ -14707,7 +14879,7 @@
       <c r="W67" s="16"/>
       <c r="X67" s="16"/>
       <c r="Y67" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.8</v>
       </c>
       <c r="Z67" s="22">
@@ -14717,13 +14889,13 @@
         <f t="shared" si="6"/>
         <v>90</v>
       </c>
-      <c r="AB67" s="24"/>
+      <c r="AB67" s="16"/>
       <c r="AC67" s="16">
         <f t="shared" si="7"/>
         <v>103.75</v>
       </c>
       <c r="AD67" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-8.75</v>
       </c>
       <c r="AE67" s="16">
@@ -14755,7 +14927,10 @@
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
-      <c r="AO67" s="16"/>
+      <c r="AO67" s="16">
+        <f t="shared" si="9"/>
+        <v>77.155555555555566</v>
+      </c>
       <c r="AP67" s="16"/>
       <c r="AQ67" s="16"/>
       <c r="AR67" s="16"/>
@@ -14796,11 +14971,11 @@
         <v>110.417</v>
       </c>
       <c r="L68" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-49.088999999999999</v>
       </c>
       <c r="M68" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>61.328000000000003</v>
       </c>
       <c r="N68" s="16"/>
@@ -14819,24 +14994,24 @@
       <c r="W68" s="16"/>
       <c r="X68" s="16"/>
       <c r="Y68" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>12.265600000000001</v>
       </c>
       <c r="Z68" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>64.145400000000009</v>
       </c>
       <c r="AA68" s="4">
         <f t="shared" si="6"/>
         <v>64.145400000000009</v>
       </c>
-      <c r="AB68" s="24"/>
+      <c r="AB68" s="16"/>
       <c r="AC68" s="16">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AD68" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.7703006783198534</v>
       </c>
       <c r="AE68" s="16">
@@ -14868,7 +15043,10 @@
         <f t="shared" si="8"/>
         <v>64</v>
       </c>
-      <c r="AO68" s="16"/>
+      <c r="AO68" s="16">
+        <f t="shared" si="9"/>
+        <v>10.745244444444445</v>
+      </c>
       <c r="AP68" s="16"/>
       <c r="AQ68" s="16"/>
       <c r="AR68" s="16"/>
@@ -14909,11 +15087,11 @@
         <v>116.342</v>
       </c>
       <c r="L69" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-32.930999999999997</v>
       </c>
       <c r="M69" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>83.411000000000001</v>
       </c>
       <c r="N69" s="16"/>
@@ -14932,24 +15110,24 @@
       <c r="W69" s="16"/>
       <c r="X69" s="16"/>
       <c r="Y69" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>16.682200000000002</v>
       </c>
       <c r="Z69" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>53.196199999999912</v>
       </c>
       <c r="AA69" s="4">
         <f t="shared" si="6"/>
         <v>53.196199999999912</v>
       </c>
-      <c r="AB69" s="24"/>
+      <c r="AB69" s="16"/>
       <c r="AC69" s="16">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AD69" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.8111999616357615</v>
       </c>
       <c r="AE69" s="16">
@@ -14981,7 +15159,10 @@
         <f t="shared" si="8"/>
         <v>53</v>
       </c>
-      <c r="AO69" s="16"/>
+      <c r="AO69" s="16">
+        <f t="shared" si="9"/>
+        <v>15.893799999999999</v>
+      </c>
       <c r="AP69" s="16"/>
       <c r="AQ69" s="16"/>
       <c r="AR69" s="16"/>
@@ -15022,11 +15203,11 @@
         <v>527</v>
       </c>
       <c r="L70" s="16">
-        <f t="shared" ref="L70:L101" si="21">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="22">E70-K70</f>
         <v>23.714000000000055</v>
       </c>
       <c r="M70" s="16">
-        <f t="shared" ref="M70:M101" si="22">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="23">E70-N70</f>
         <v>550.71400000000006</v>
       </c>
       <c r="N70" s="16"/>
@@ -15045,24 +15226,24 @@
       <c r="W70" s="16"/>
       <c r="X70" s="16"/>
       <c r="Y70" s="16">
-        <f t="shared" ref="Y70:Y101" si="23">M70/5</f>
+        <f t="shared" ref="Y70:Y101" si="24">M70/5</f>
         <v>110.14280000000001</v>
       </c>
       <c r="Z70" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>183.71392000000014</v>
       </c>
-      <c r="AA70" s="31">
+      <c r="AA70" s="29">
         <f>Z70+$AA$1*Y70</f>
         <v>392.98524000000015</v>
       </c>
-      <c r="AB70" s="24"/>
+      <c r="AB70" s="16"/>
       <c r="AC70" s="16">
         <f t="shared" si="7"/>
         <v>12.900000000000002</v>
       </c>
       <c r="AD70" s="16">
-        <f t="shared" ref="AD70:AD101" si="24">(F70+O70+P70+Q70+R70+S70+T70+U70+V70+W70+X70)/Y70</f>
+        <f t="shared" ref="AD70:AD101" si="25">(F70+O70+P70+Q70+R70+S70+T70+U70+V70+W70+X70)/Y70</f>
         <v>9.3320387714857436</v>
       </c>
       <c r="AE70" s="16">
@@ -15094,7 +15275,10 @@
         <f t="shared" si="8"/>
         <v>393</v>
       </c>
-      <c r="AO70" s="16"/>
+      <c r="AO70" s="16">
+        <f t="shared" si="9"/>
+        <v>134.15115555555556</v>
+      </c>
       <c r="AP70" s="16"/>
       <c r="AQ70" s="16"/>
       <c r="AR70" s="16"/>
@@ -15133,11 +15317,11 @@
         <v>102.5</v>
       </c>
       <c r="L71" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-8.0450000000000017</v>
       </c>
       <c r="M71" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>94.454999999999998</v>
       </c>
       <c r="N71" s="16"/>
@@ -15156,7 +15340,7 @@
       <c r="W71" s="16"/>
       <c r="X71" s="16"/>
       <c r="Y71" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>18.890999999999998</v>
       </c>
       <c r="Z71" s="4">
@@ -15164,16 +15348,16 @@
         <v>117.58580000000001</v>
       </c>
       <c r="AA71" s="4">
-        <f t="shared" ref="AA71:AA134" si="25">Z71</f>
+        <f t="shared" ref="AA71:AA134" si="26">Z71</f>
         <v>117.58580000000001</v>
       </c>
-      <c r="AB71" s="24"/>
+      <c r="AB71" s="16"/>
       <c r="AC71" s="16">
-        <f t="shared" ref="AC71:AC134" si="26">(F71+O71+P71+Q71+R71+S71+T71+U71+V71+W71+X71+AA71)/Y71</f>
+        <f t="shared" ref="AC71:AC134" si="27">(F71+O71+P71+Q71+R71+S71+T71+U71+V71+W71+X71+AA71)/Y71</f>
         <v>7</v>
       </c>
       <c r="AD71" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.77556508390238688</v>
       </c>
       <c r="AE71" s="16">
@@ -15202,10 +15386,13 @@
       </c>
       <c r="AM71" s="16"/>
       <c r="AN71" s="16">
-        <f t="shared" ref="AN71:AN134" si="27">ROUND(G71*AA71,0)</f>
+        <f t="shared" ref="AN71:AN134" si="28">ROUND(G71*AA71,0)</f>
         <v>118</v>
       </c>
-      <c r="AO71" s="16"/>
+      <c r="AO71" s="16">
+        <f t="shared" ref="AO71:AO134" si="29">(SUM(AE71:AL71)+Y71)/9</f>
+        <v>10.90248888888889</v>
+      </c>
       <c r="AP71" s="16"/>
       <c r="AQ71" s="16"/>
       <c r="AR71" s="16"/>
@@ -15234,11 +15421,11 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M72" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N72" s="10"/>
@@ -15257,21 +15444,21 @@
       <c r="W72" s="10"/>
       <c r="X72" s="10"/>
       <c r="Y72" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z72" s="12"/>
       <c r="AA72" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB72" s="16"/>
+      <c r="AC72" s="16" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD72" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB72" s="24"/>
-      <c r="AC72" s="16" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD72" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE72" s="10">
@@ -15302,10 +15489,13 @@
         <v>64</v>
       </c>
       <c r="AN72" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO72" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO72" s="16">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AP72" s="16"/>
       <c r="AQ72" s="16"/>
       <c r="AR72" s="16"/>
@@ -15346,11 +15536,11 @@
         <v>544.20000000000005</v>
       </c>
       <c r="L73" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-45.03000000000003</v>
       </c>
       <c r="M73" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>499.17</v>
       </c>
       <c r="N73" s="16"/>
@@ -15371,21 +15561,21 @@
       </c>
       <c r="X73" s="16"/>
       <c r="Y73" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>99.834000000000003</v>
       </c>
       <c r="Z73" s="4"/>
       <c r="AA73" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB73" s="16"/>
+      <c r="AC73" s="16">
+        <f t="shared" si="27"/>
+        <v>11.985743153635035</v>
+      </c>
+      <c r="AD73" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB73" s="24"/>
-      <c r="AC73" s="16">
-        <f t="shared" si="26"/>
-        <v>11.985743153635035</v>
-      </c>
-      <c r="AD73" s="16">
-        <f t="shared" si="24"/>
         <v>11.985743153635035</v>
       </c>
       <c r="AE73" s="16">
@@ -15414,10 +15604,13 @@
       </c>
       <c r="AM73" s="16"/>
       <c r="AN73" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO73" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO73" s="16">
+        <f t="shared" si="29"/>
+        <v>91.630533333333332</v>
+      </c>
       <c r="AP73" s="16"/>
       <c r="AQ73" s="16"/>
       <c r="AR73" s="16"/>
@@ -15458,11 +15651,11 @@
         <v>586</v>
       </c>
       <c r="L74" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-189</v>
       </c>
       <c r="M74" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>397</v>
       </c>
       <c r="N74" s="16"/>
@@ -15485,23 +15678,23 @@
       </c>
       <c r="X74" s="16"/>
       <c r="Y74" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>79.400000000000006</v>
       </c>
       <c r="Z74" s="4"/>
       <c r="AA74" s="4">
         <v>100</v>
       </c>
-      <c r="AB74" s="24" t="str">
+      <c r="AB74" s="16" t="str">
         <f>VLOOKUP(A74,[1]Sheet!$A:$AA,27,0)</f>
         <v>300 увеличить запас</v>
       </c>
       <c r="AC74" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>23.110931989924431</v>
       </c>
       <c r="AD74" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>21.851486146095716</v>
       </c>
       <c r="AE74" s="16">
@@ -15530,10 +15723,13 @@
       </c>
       <c r="AM74" s="16"/>
       <c r="AN74" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
-      <c r="AO74" s="16"/>
+      <c r="AO74" s="16">
+        <f t="shared" si="29"/>
+        <v>101.42222222222223</v>
+      </c>
       <c r="AP74" s="16"/>
       <c r="AQ74" s="16"/>
       <c r="AR74" s="16"/>
@@ -15574,11 +15770,11 @@
         <v>569</v>
       </c>
       <c r="L75" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-85</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>484</v>
       </c>
       <c r="N75" s="16"/>
@@ -15601,23 +15797,23 @@
       </c>
       <c r="X75" s="16"/>
       <c r="Y75" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>96.8</v>
       </c>
       <c r="Z75" s="4"/>
       <c r="AA75" s="4">
         <v>100</v>
       </c>
-      <c r="AB75" s="24" t="str">
+      <c r="AB75" s="16" t="str">
         <f>VLOOKUP(A75,[1]Sheet!$A:$AA,27,0)</f>
         <v>300  увеличить запас</v>
       </c>
       <c r="AC75" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16.691033057851239</v>
       </c>
       <c r="AD75" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>15.657975206611571</v>
       </c>
       <c r="AE75" s="16">
@@ -15646,10 +15842,13 @@
       </c>
       <c r="AM75" s="16"/>
       <c r="AN75" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
-      <c r="AO75" s="16"/>
+      <c r="AO75" s="16">
+        <f t="shared" si="29"/>
+        <v>95.600000000000009</v>
+      </c>
       <c r="AP75" s="16"/>
       <c r="AQ75" s="16"/>
       <c r="AR75" s="16"/>
@@ -15678,11 +15877,11 @@
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
       <c r="L76" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M76" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N76" s="10"/>
@@ -15701,21 +15900,21 @@
       <c r="W76" s="10"/>
       <c r="X76" s="10"/>
       <c r="Y76" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z76" s="12"/>
       <c r="AA76" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB76" s="16"/>
+      <c r="AC76" s="16" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD76" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB76" s="24"/>
-      <c r="AC76" s="16" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD76" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE76" s="10">
@@ -15746,10 +15945,13 @@
         <v>64</v>
       </c>
       <c r="AN76" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO76" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO76" s="16">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AP76" s="16"/>
       <c r="AQ76" s="16"/>
       <c r="AR76" s="16"/>
@@ -15784,11 +15986,11 @@
         <v>3</v>
       </c>
       <c r="L77" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-3</v>
       </c>
       <c r="M77" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N77" s="10"/>
@@ -15807,21 +16009,21 @@
       <c r="W77" s="10"/>
       <c r="X77" s="10"/>
       <c r="Y77" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z77" s="12"/>
       <c r="AA77" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB77" s="16"/>
+      <c r="AC77" s="16" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD77" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB77" s="24"/>
-      <c r="AC77" s="16" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD77" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE77" s="10">
@@ -15852,10 +16054,13 @@
         <v>64</v>
       </c>
       <c r="AN77" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO77" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO77" s="16">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AP77" s="16"/>
       <c r="AQ77" s="16"/>
       <c r="AR77" s="16"/>
@@ -15896,11 +16101,11 @@
         <v>62</v>
       </c>
       <c r="L78" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-10</v>
       </c>
       <c r="M78" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>52</v>
       </c>
       <c r="N78" s="16"/>
@@ -15919,24 +16124,24 @@
       <c r="W78" s="16"/>
       <c r="X78" s="16"/>
       <c r="Y78" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.4</v>
       </c>
       <c r="Z78" s="4">
-        <f t="shared" ref="Z78" si="28">11*Y78-X78-W78-V78-U78-T78-S78-R78-Q78-P78-O78-F78</f>
+        <f t="shared" ref="Z78" si="30">11*Y78-X78-W78-V78-U78-T78-S78-R78-Q78-P78-O78-F78</f>
         <v>45.400000000000006</v>
       </c>
       <c r="AA78" s="4">
+        <f t="shared" si="26"/>
+        <v>45.400000000000006</v>
+      </c>
+      <c r="AB78" s="16"/>
+      <c r="AC78" s="16">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="AD78" s="16">
         <f t="shared" si="25"/>
-        <v>45.400000000000006</v>
-      </c>
-      <c r="AB78" s="24"/>
-      <c r="AC78" s="16">
-        <f t="shared" si="26"/>
-        <v>11</v>
-      </c>
-      <c r="AD78" s="16">
-        <f t="shared" si="24"/>
         <v>6.6346153846153841</v>
       </c>
       <c r="AE78" s="16">
@@ -15965,10 +16170,13 @@
       </c>
       <c r="AM78" s="16"/>
       <c r="AN78" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>16</v>
       </c>
-      <c r="AO78" s="16"/>
+      <c r="AO78" s="16">
+        <f t="shared" si="29"/>
+        <v>10.133333333333333</v>
+      </c>
       <c r="AP78" s="16"/>
       <c r="AQ78" s="16"/>
       <c r="AR78" s="16"/>
@@ -16009,11 +16217,11 @@
         <v>121</v>
       </c>
       <c r="L79" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-40</v>
       </c>
       <c r="M79" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>81</v>
       </c>
       <c r="N79" s="16"/>
@@ -16032,21 +16240,21 @@
       <c r="W79" s="16"/>
       <c r="X79" s="16"/>
       <c r="Y79" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>16.2</v>
       </c>
       <c r="Z79" s="4"/>
       <c r="AA79" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB79" s="16"/>
+      <c r="AC79" s="16">
+        <f t="shared" si="27"/>
+        <v>18.407407407407408</v>
+      </c>
+      <c r="AD79" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB79" s="24"/>
-      <c r="AC79" s="16">
-        <f t="shared" si="26"/>
-        <v>18.407407407407408</v>
-      </c>
-      <c r="AD79" s="16">
-        <f t="shared" si="24"/>
         <v>18.407407407407408</v>
       </c>
       <c r="AE79" s="16">
@@ -16075,10 +16283,13 @@
       </c>
       <c r="AM79" s="16"/>
       <c r="AN79" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO79" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO79" s="16">
+        <f t="shared" si="29"/>
+        <v>27.333333333333332</v>
+      </c>
       <c r="AP79" s="16"/>
       <c r="AQ79" s="16"/>
       <c r="AR79" s="16"/>
@@ -16119,11 +16330,11 @@
         <v>649</v>
       </c>
       <c r="L80" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-231</v>
       </c>
       <c r="M80" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>418</v>
       </c>
       <c r="N80" s="16"/>
@@ -16144,7 +16355,7 @@
       </c>
       <c r="X80" s="16"/>
       <c r="Y80" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>83.6</v>
       </c>
       <c r="Z80" s="4">
@@ -16154,16 +16365,16 @@
       <c r="AA80" s="4">
         <v>300</v>
       </c>
-      <c r="AB80" s="24" t="str">
+      <c r="AB80" s="16" t="str">
         <f>VLOOKUP(A80,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить запас </v>
       </c>
       <c r="AC80" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.303827751196174</v>
       </c>
       <c r="AD80" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7.7153110047846898</v>
       </c>
       <c r="AE80" s="16">
@@ -16194,10 +16405,13 @@
         <v>129</v>
       </c>
       <c r="AN80" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>180</v>
       </c>
-      <c r="AO80" s="16"/>
+      <c r="AO80" s="16">
+        <f t="shared" si="29"/>
+        <v>149.29437777777778</v>
+      </c>
       <c r="AP80" s="16"/>
       <c r="AQ80" s="16"/>
       <c r="AR80" s="16"/>
@@ -16238,11 +16452,11 @@
         <v>284</v>
       </c>
       <c r="L81" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-29</v>
       </c>
       <c r="M81" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>255</v>
       </c>
       <c r="N81" s="16"/>
@@ -16263,7 +16477,7 @@
       <c r="W81" s="16"/>
       <c r="X81" s="16"/>
       <c r="Y81" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>51</v>
       </c>
       <c r="Z81" s="4">
@@ -16271,16 +16485,16 @@
         <v>206.86</v>
       </c>
       <c r="AA81" s="4">
+        <f t="shared" si="26"/>
+        <v>206.86</v>
+      </c>
+      <c r="AB81" s="16"/>
+      <c r="AC81" s="16">
+        <f t="shared" si="27"/>
+        <v>7</v>
+      </c>
+      <c r="AD81" s="16">
         <f t="shared" si="25"/>
-        <v>206.86</v>
-      </c>
-      <c r="AB81" s="24"/>
-      <c r="AC81" s="16">
-        <f t="shared" si="26"/>
-        <v>7</v>
-      </c>
-      <c r="AD81" s="16">
-        <f t="shared" si="24"/>
         <v>2.9439215686274509</v>
       </c>
       <c r="AE81" s="16">
@@ -16309,10 +16523,13 @@
       </c>
       <c r="AM81" s="16"/>
       <c r="AN81" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>68</v>
       </c>
-      <c r="AO81" s="16"/>
+      <c r="AO81" s="16">
+        <f t="shared" si="29"/>
+        <v>34.844444444444441</v>
+      </c>
       <c r="AP81" s="16"/>
       <c r="AQ81" s="16"/>
       <c r="AR81" s="16"/>
@@ -16353,11 +16570,11 @@
         <v>58</v>
       </c>
       <c r="L82" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-4</v>
       </c>
       <c r="M82" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>54</v>
       </c>
       <c r="N82" s="16"/>
@@ -16376,21 +16593,21 @@
       <c r="W82" s="16"/>
       <c r="X82" s="16"/>
       <c r="Y82" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.8</v>
       </c>
       <c r="Z82" s="4"/>
       <c r="AA82" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB82" s="16"/>
+      <c r="AC82" s="16">
+        <f t="shared" si="27"/>
+        <v>11.879629629629628</v>
+      </c>
+      <c r="AD82" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB82" s="24"/>
-      <c r="AC82" s="16">
-        <f t="shared" si="26"/>
-        <v>11.879629629629628</v>
-      </c>
-      <c r="AD82" s="16">
-        <f t="shared" si="24"/>
         <v>11.879629629629628</v>
       </c>
       <c r="AE82" s="16">
@@ -16419,10 +16636,13 @@
       </c>
       <c r="AM82" s="16"/>
       <c r="AN82" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO82" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO82" s="16">
+        <f t="shared" si="29"/>
+        <v>10.044444444444444</v>
+      </c>
       <c r="AP82" s="16"/>
       <c r="AQ82" s="16"/>
       <c r="AR82" s="16"/>
@@ -16463,11 +16683,11 @@
         <v>30</v>
       </c>
       <c r="L83" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-35</v>
       </c>
       <c r="M83" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-5</v>
       </c>
       <c r="N83" s="16"/>
@@ -16488,21 +16708,21 @@
       <c r="W83" s="16"/>
       <c r="X83" s="16"/>
       <c r="Y83" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-1</v>
       </c>
       <c r="Z83" s="4"/>
       <c r="AA83" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB83" s="16"/>
+      <c r="AC83" s="16">
+        <f t="shared" si="27"/>
+        <v>-293</v>
+      </c>
+      <c r="AD83" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB83" s="24"/>
-      <c r="AC83" s="16">
-        <f t="shared" si="26"/>
-        <v>-293</v>
-      </c>
-      <c r="AD83" s="16">
-        <f t="shared" si="24"/>
         <v>-293</v>
       </c>
       <c r="AE83" s="16">
@@ -16531,10 +16751,13 @@
       </c>
       <c r="AM83" s="16"/>
       <c r="AN83" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO83" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO83" s="16">
+        <f t="shared" si="29"/>
+        <v>29.911111111111111</v>
+      </c>
       <c r="AP83" s="16"/>
       <c r="AQ83" s="16"/>
       <c r="AR83" s="16"/>
@@ -16571,11 +16794,11 @@
         <v>451</v>
       </c>
       <c r="L84" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-65</v>
       </c>
       <c r="M84" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>386</v>
       </c>
       <c r="N84" s="16"/>
@@ -16596,7 +16819,7 @@
       <c r="W84" s="16"/>
       <c r="X84" s="16"/>
       <c r="Y84" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>77.2</v>
       </c>
       <c r="Z84" s="4">
@@ -16604,16 +16827,16 @@
         <v>463.20000000000005</v>
       </c>
       <c r="AA84" s="4">
+        <f t="shared" si="26"/>
+        <v>463.20000000000005</v>
+      </c>
+      <c r="AB84" s="16"/>
+      <c r="AC84" s="16">
+        <f t="shared" si="27"/>
+        <v>6</v>
+      </c>
+      <c r="AD84" s="16">
         <f t="shared" si="25"/>
-        <v>463.20000000000005</v>
-      </c>
-      <c r="AB84" s="24"/>
-      <c r="AC84" s="16">
-        <f t="shared" si="26"/>
-        <v>6</v>
-      </c>
-      <c r="AD84" s="16">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AE84" s="16">
@@ -16642,10 +16865,13 @@
       </c>
       <c r="AM84" s="16"/>
       <c r="AN84" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162</v>
       </c>
-      <c r="AO84" s="16"/>
+      <c r="AO84" s="16">
+        <f t="shared" si="29"/>
+        <v>70.62222222222222</v>
+      </c>
       <c r="AP84" s="16"/>
       <c r="AQ84" s="16"/>
       <c r="AR84" s="16"/>
@@ -16684,11 +16910,11 @@
         <v>40</v>
       </c>
       <c r="L85" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
       <c r="M85" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>38</v>
       </c>
       <c r="N85" s="16"/>
@@ -16707,7 +16933,7 @@
       <c r="W85" s="16"/>
       <c r="X85" s="16"/>
       <c r="Y85" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.6</v>
       </c>
       <c r="Z85" s="4">
@@ -16715,16 +16941,16 @@
         <v>48</v>
       </c>
       <c r="AA85" s="4">
+        <f t="shared" si="26"/>
+        <v>48</v>
+      </c>
+      <c r="AB85" s="16"/>
+      <c r="AC85" s="16">
+        <f t="shared" si="27"/>
+        <v>10</v>
+      </c>
+      <c r="AD85" s="16">
         <f t="shared" si="25"/>
-        <v>48</v>
-      </c>
-      <c r="AB85" s="24"/>
-      <c r="AC85" s="16">
-        <f t="shared" si="26"/>
-        <v>10</v>
-      </c>
-      <c r="AD85" s="16">
-        <f t="shared" si="24"/>
         <v>3.6842105263157898</v>
       </c>
       <c r="AE85" s="16">
@@ -16753,10 +16979,13 @@
       </c>
       <c r="AM85" s="16"/>
       <c r="AN85" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>19</v>
       </c>
-      <c r="AO85" s="16"/>
+      <c r="AO85" s="16">
+        <f t="shared" si="29"/>
+        <v>2.9555555555555557</v>
+      </c>
       <c r="AP85" s="16"/>
       <c r="AQ85" s="16"/>
       <c r="AR85" s="16"/>
@@ -16797,11 +17026,11 @@
         <v>7.9</v>
       </c>
       <c r="L86" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.69200000000000017</v>
       </c>
       <c r="M86" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.5920000000000005</v>
       </c>
       <c r="N86" s="16"/>
@@ -16820,21 +17049,21 @@
       <c r="W86" s="16"/>
       <c r="X86" s="16"/>
       <c r="Y86" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.7184000000000001</v>
       </c>
       <c r="Z86" s="4"/>
       <c r="AA86" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB86" s="16"/>
+      <c r="AC86" s="16">
+        <f t="shared" si="27"/>
+        <v>26.262220670391059</v>
+      </c>
+      <c r="AD86" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB86" s="24"/>
-      <c r="AC86" s="16">
-        <f t="shared" si="26"/>
-        <v>26.262220670391059</v>
-      </c>
-      <c r="AD86" s="16">
-        <f t="shared" si="24"/>
         <v>26.262220670391059</v>
       </c>
       <c r="AE86" s="16">
@@ -16865,10 +17094,13 @@
         <v>136</v>
       </c>
       <c r="AN86" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO86" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO86" s="16">
+        <f t="shared" si="29"/>
+        <v>1.7908444444444445</v>
+      </c>
       <c r="AP86" s="16"/>
       <c r="AQ86" s="16"/>
       <c r="AR86" s="16"/>
@@ -16897,11 +17129,11 @@
       <c r="J87" s="10"/>
       <c r="K87" s="10"/>
       <c r="L87" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M87" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N87" s="10"/>
@@ -16920,21 +17152,21 @@
       <c r="W87" s="10"/>
       <c r="X87" s="10"/>
       <c r="Y87" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z87" s="12"/>
       <c r="AA87" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB87" s="16"/>
+      <c r="AC87" s="16" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD87" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB87" s="24"/>
-      <c r="AC87" s="16" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD87" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE87" s="10">
@@ -16965,10 +17197,13 @@
         <v>64</v>
       </c>
       <c r="AN87" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO87" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO87" s="16">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AP87" s="16"/>
       <c r="AQ87" s="16"/>
       <c r="AR87" s="16"/>
@@ -17009,11 +17244,11 @@
         <v>2614.9499999999998</v>
       </c>
       <c r="L88" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8.3500000000003638</v>
       </c>
       <c r="M88" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2623.3</v>
       </c>
       <c r="N88" s="16"/>
@@ -17036,24 +17271,24 @@
       </c>
       <c r="X88" s="16"/>
       <c r="Y88" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>524.66000000000008</v>
       </c>
       <c r="Z88" s="4">
-        <f t="shared" ref="Z88:Z90" si="29">11*Y88-X88-W88-V88-U88-T88-S88-R88-Q88-P88-O88-F88</f>
+        <f t="shared" ref="Z88:Z90" si="31">11*Y88-X88-W88-V88-U88-T88-S88-R88-Q88-P88-O88-F88</f>
         <v>415.7517640000018</v>
       </c>
-      <c r="AA88" s="31">
+      <c r="AA88" s="29">
         <f>Z88+$AA$1*Y88</f>
         <v>1412.605764000002</v>
       </c>
-      <c r="AB88" s="24"/>
+      <c r="AB88" s="16"/>
       <c r="AC88" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12.9</v>
       </c>
       <c r="AD88" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>10.207578690961764</v>
       </c>
       <c r="AE88" s="16">
@@ -17082,10 +17317,13 @@
       </c>
       <c r="AM88" s="16"/>
       <c r="AN88" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1413</v>
       </c>
-      <c r="AO88" s="16"/>
+      <c r="AO88" s="16">
+        <f t="shared" si="29"/>
+        <v>578.27477777777779</v>
+      </c>
       <c r="AP88" s="16"/>
       <c r="AQ88" s="16"/>
       <c r="AR88" s="16"/>
@@ -17126,11 +17364,11 @@
         <v>207</v>
       </c>
       <c r="L89" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-28</v>
       </c>
       <c r="M89" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>179</v>
       </c>
       <c r="N89" s="16"/>
@@ -17151,21 +17389,21 @@
       <c r="W89" s="16"/>
       <c r="X89" s="16"/>
       <c r="Y89" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>35.799999999999997</v>
       </c>
       <c r="Z89" s="4"/>
       <c r="AA89" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB89" s="16"/>
+      <c r="AC89" s="16">
+        <f t="shared" si="27"/>
+        <v>13.882681564245811</v>
+      </c>
+      <c r="AD89" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB89" s="24"/>
-      <c r="AC89" s="16">
-        <f t="shared" si="26"/>
-        <v>13.882681564245811</v>
-      </c>
-      <c r="AD89" s="16">
-        <f t="shared" si="24"/>
         <v>13.882681564245811</v>
       </c>
       <c r="AE89" s="16">
@@ -17194,10 +17432,13 @@
       </c>
       <c r="AM89" s="16"/>
       <c r="AN89" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO89" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO89" s="16">
+        <f t="shared" si="29"/>
+        <v>36.911111111111111</v>
+      </c>
       <c r="AP89" s="16"/>
       <c r="AQ89" s="16"/>
       <c r="AR89" s="16"/>
@@ -17238,11 +17479,11 @@
         <v>1236</v>
       </c>
       <c r="L90" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-58.794000000000096</v>
       </c>
       <c r="M90" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1177.2059999999999</v>
       </c>
       <c r="N90" s="16"/>
@@ -17265,24 +17506,24 @@
       </c>
       <c r="X90" s="16"/>
       <c r="Y90" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>235.44119999999998</v>
       </c>
       <c r="Z90" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>63.674611999999108</v>
       </c>
-      <c r="AA90" s="31">
+      <c r="AA90" s="29">
         <f>Z90+$AA$1*Y90</f>
         <v>511.01289199999906</v>
       </c>
-      <c r="AB90" s="24"/>
+      <c r="AB90" s="16"/>
       <c r="AC90" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12.899999999999999</v>
       </c>
       <c r="AD90" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>10.729551956072262</v>
       </c>
       <c r="AE90" s="16">
@@ -17311,10 +17552,13 @@
       </c>
       <c r="AM90" s="16"/>
       <c r="AN90" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>511</v>
       </c>
-      <c r="AO90" s="16"/>
+      <c r="AO90" s="16">
+        <f t="shared" si="29"/>
+        <v>243.51200000000003</v>
+      </c>
       <c r="AP90" s="16"/>
       <c r="AQ90" s="16"/>
       <c r="AR90" s="16"/>
@@ -17355,11 +17599,11 @@
         <v>2643.2840000000001</v>
       </c>
       <c r="L91" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-102.76200000000017</v>
       </c>
       <c r="M91" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2239.538</v>
       </c>
       <c r="N91" s="16">
@@ -17388,21 +17632,21 @@
         <v>1000</v>
       </c>
       <c r="Y91" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>447.9076</v>
       </c>
       <c r="Z91" s="4"/>
       <c r="AA91" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB91" s="16"/>
+      <c r="AC91" s="16">
+        <f t="shared" si="27"/>
+        <v>20.291075659354743</v>
+      </c>
+      <c r="AD91" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB91" s="24"/>
-      <c r="AC91" s="16">
-        <f t="shared" si="26"/>
-        <v>20.291075659354743</v>
-      </c>
-      <c r="AD91" s="16">
-        <f t="shared" si="24"/>
         <v>20.291075659354743</v>
       </c>
       <c r="AE91" s="16">
@@ -17433,10 +17677,13 @@
         <v>92</v>
       </c>
       <c r="AN91" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO91" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO91" s="16">
+        <f t="shared" si="29"/>
+        <v>532.69362222222219</v>
+      </c>
       <c r="AP91" s="16"/>
       <c r="AQ91" s="16"/>
       <c r="AR91" s="16"/>
@@ -17478,11 +17725,11 @@
         <v>4002.904</v>
       </c>
       <c r="L92" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-100.78999999999996</v>
       </c>
       <c r="M92" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3589.41</v>
       </c>
       <c r="N92" s="16">
@@ -17509,21 +17756,21 @@
       <c r="W92" s="16"/>
       <c r="X92" s="16"/>
       <c r="Y92" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>717.88199999999995</v>
       </c>
       <c r="Z92" s="4"/>
       <c r="AA92" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB92" s="16"/>
+      <c r="AC92" s="16">
+        <f t="shared" si="27"/>
+        <v>15.133548410463</v>
+      </c>
+      <c r="AD92" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB92" s="24"/>
-      <c r="AC92" s="16">
-        <f t="shared" si="26"/>
-        <v>15.133548410463</v>
-      </c>
-      <c r="AD92" s="16">
-        <f t="shared" si="24"/>
         <v>15.133548410463</v>
       </c>
       <c r="AE92" s="16">
@@ -17552,10 +17799,13 @@
       </c>
       <c r="AM92" s="16"/>
       <c r="AN92" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO92" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO92" s="16">
+        <f t="shared" si="29"/>
+        <v>663.94031111111099</v>
+      </c>
       <c r="AP92" s="16"/>
       <c r="AQ92" s="16"/>
       <c r="AR92" s="16"/>
@@ -17596,11 +17846,11 @@
         <v>39</v>
       </c>
       <c r="L93" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-14.956</v>
       </c>
       <c r="M93" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>24.044</v>
       </c>
       <c r="N93" s="16"/>
@@ -17619,21 +17869,21 @@
       <c r="W93" s="16"/>
       <c r="X93" s="16"/>
       <c r="Y93" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.8087999999999997</v>
       </c>
       <c r="Z93" s="4"/>
       <c r="AA93" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB93" s="16"/>
+      <c r="AC93" s="16">
+        <f t="shared" si="27"/>
+        <v>18.765804358675762</v>
+      </c>
+      <c r="AD93" s="16">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB93" s="24"/>
-      <c r="AC93" s="16">
-        <f t="shared" si="26"/>
-        <v>18.765804358675762</v>
-      </c>
-      <c r="AD93" s="16">
-        <f t="shared" si="24"/>
         <v>18.765804358675762</v>
       </c>
       <c r="AE93" s="16">
@@ -17664,10 +17914,13 @@
         <v>136</v>
       </c>
       <c r="AN93" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO93" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO93" s="16">
+        <f t="shared" si="29"/>
+        <v>8.1687111111111115</v>
+      </c>
       <c r="AP93" s="16"/>
       <c r="AQ93" s="16"/>
       <c r="AR93" s="16"/>
@@ -17700,11 +17953,11 @@
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
       <c r="L94" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M94" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N94" s="10"/>
@@ -17723,21 +17976,21 @@
       <c r="W94" s="10"/>
       <c r="X94" s="10"/>
       <c r="Y94" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z94" s="12"/>
       <c r="AA94" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB94" s="16"/>
+      <c r="AC94" s="16" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD94" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB94" s="24"/>
-      <c r="AC94" s="16" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD94" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE94" s="10">
@@ -17766,10 +18019,13 @@
       </c>
       <c r="AM94" s="10"/>
       <c r="AN94" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO94" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO94" s="16">
+        <f t="shared" si="29"/>
+        <v>6.0444444444444446E-2</v>
+      </c>
       <c r="AP94" s="16"/>
       <c r="AQ94" s="16"/>
       <c r="AR94" s="16"/>
@@ -17808,11 +18064,11 @@
         <v>26</v>
       </c>
       <c r="L95" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.89199999999999946</v>
       </c>
       <c r="M95" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>26.891999999999999</v>
       </c>
       <c r="N95" s="10"/>
@@ -17831,21 +18087,21 @@
       <c r="W95" s="10"/>
       <c r="X95" s="10"/>
       <c r="Y95" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.3784000000000001</v>
       </c>
       <c r="Z95" s="12"/>
       <c r="AA95" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB95" s="16"/>
+      <c r="AC95" s="16">
+        <f t="shared" si="27"/>
+        <v>74.781719470474499</v>
+      </c>
+      <c r="AD95" s="10">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB95" s="24"/>
-      <c r="AC95" s="16">
-        <f t="shared" si="26"/>
-        <v>74.781719470474499</v>
-      </c>
-      <c r="AD95" s="10">
-        <f t="shared" si="24"/>
         <v>74.781719470474499</v>
       </c>
       <c r="AE95" s="10">
@@ -17876,10 +18132,13 @@
         <v>136</v>
       </c>
       <c r="AN95" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO95" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO95" s="16">
+        <f t="shared" si="29"/>
+        <v>8.1587777777777788</v>
+      </c>
       <c r="AP95" s="16"/>
       <c r="AQ95" s="16"/>
       <c r="AR95" s="16"/>
@@ -17920,11 +18179,11 @@
         <v>183</v>
       </c>
       <c r="L96" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-107</v>
       </c>
       <c r="M96" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>76</v>
       </c>
       <c r="N96" s="16"/>
@@ -17943,24 +18202,24 @@
       <c r="W96" s="16"/>
       <c r="X96" s="16"/>
       <c r="Y96" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15.2</v>
       </c>
       <c r="Z96" s="4">
-        <f t="shared" ref="Z96:Z100" si="30">11*Y96-X96-W96-V96-U96-T96-S96-R96-Q96-P96-O96-F96</f>
+        <f t="shared" ref="Z96:Z100" si="32">11*Y96-X96-W96-V96-U96-T96-S96-R96-Q96-P96-O96-F96</f>
         <v>68.900000000000006</v>
       </c>
       <c r="AA96" s="4">
+        <f t="shared" si="26"/>
+        <v>68.900000000000006</v>
+      </c>
+      <c r="AB96" s="16"/>
+      <c r="AC96" s="16">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="AD96" s="16">
         <f t="shared" si="25"/>
-        <v>68.900000000000006</v>
-      </c>
-      <c r="AB96" s="24"/>
-      <c r="AC96" s="16">
-        <f t="shared" si="26"/>
-        <v>11</v>
-      </c>
-      <c r="AD96" s="16">
-        <f t="shared" si="24"/>
         <v>6.4671052631578938</v>
       </c>
       <c r="AE96" s="16">
@@ -17989,10 +18248,13 @@
       </c>
       <c r="AM96" s="16"/>
       <c r="AN96" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>21</v>
       </c>
-      <c r="AO96" s="16"/>
+      <c r="AO96" s="16">
+        <f t="shared" si="29"/>
+        <v>20.266666666666666</v>
+      </c>
       <c r="AP96" s="16"/>
       <c r="AQ96" s="16"/>
       <c r="AR96" s="16"/>
@@ -18033,11 +18295,11 @@
         <v>51</v>
       </c>
       <c r="L97" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-3</v>
       </c>
       <c r="M97" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>48</v>
       </c>
       <c r="N97" s="16"/>
@@ -18056,24 +18318,24 @@
       <c r="W97" s="16"/>
       <c r="X97" s="16"/>
       <c r="Y97" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.6</v>
       </c>
       <c r="Z97" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>45.999999999999986</v>
       </c>
       <c r="AA97" s="4">
+        <f t="shared" si="26"/>
+        <v>45.999999999999986</v>
+      </c>
+      <c r="AB97" s="16"/>
+      <c r="AC97" s="16">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="AD97" s="16">
         <f t="shared" si="25"/>
-        <v>45.999999999999986</v>
-      </c>
-      <c r="AB97" s="24"/>
-      <c r="AC97" s="16">
-        <f t="shared" si="26"/>
-        <v>11</v>
-      </c>
-      <c r="AD97" s="16">
-        <f t="shared" si="24"/>
         <v>6.2083333333333348</v>
       </c>
       <c r="AE97" s="16">
@@ -18102,10 +18364,13 @@
       </c>
       <c r="AM97" s="16"/>
       <c r="AN97" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>14</v>
       </c>
-      <c r="AO97" s="16"/>
+      <c r="AO97" s="16">
+        <f t="shared" si="29"/>
+        <v>7.133333333333332</v>
+      </c>
       <c r="AP97" s="16"/>
       <c r="AQ97" s="16"/>
       <c r="AR97" s="16"/>
@@ -18146,11 +18411,11 @@
         <v>184</v>
       </c>
       <c r="L98" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-22</v>
       </c>
       <c r="M98" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>162</v>
       </c>
       <c r="N98" s="16"/>
@@ -18171,26 +18436,26 @@
       <c r="W98" s="16"/>
       <c r="X98" s="16"/>
       <c r="Y98" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>32.4</v>
       </c>
       <c r="Z98" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>33.300000000000026</v>
       </c>
       <c r="AA98" s="4">
         <v>330</v>
       </c>
-      <c r="AB98" s="24" t="str">
+      <c r="AB98" s="16" t="str">
         <f>VLOOKUP(A98,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC98" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20.157407407407405</v>
       </c>
       <c r="AD98" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.9722222222222214</v>
       </c>
       <c r="AE98" s="16">
@@ -18221,10 +18486,13 @@
         <v>189</v>
       </c>
       <c r="AN98" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>23</v>
       </c>
-      <c r="AO98" s="16"/>
+      <c r="AO98" s="16">
+        <f t="shared" si="29"/>
+        <v>28.599999999999998</v>
+      </c>
       <c r="AP98" s="16"/>
       <c r="AQ98" s="16"/>
       <c r="AR98" s="16"/>
@@ -18265,11 +18533,11 @@
         <v>150</v>
       </c>
       <c r="L99" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-9</v>
       </c>
       <c r="M99" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>141</v>
       </c>
       <c r="N99" s="16"/>
@@ -18288,26 +18556,26 @@
       <c r="W99" s="16"/>
       <c r="X99" s="16"/>
       <c r="Y99" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>28.2</v>
       </c>
       <c r="Z99" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>85.97999999999999</v>
       </c>
       <c r="AA99" s="4">
         <v>390</v>
       </c>
-      <c r="AB99" s="24" t="str">
+      <c r="AB99" s="16" t="str">
         <f>VLOOKUP(A99,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC99" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21.78085106382979</v>
       </c>
       <c r="AD99" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7.951063829787234</v>
       </c>
       <c r="AE99" s="16">
@@ -18338,10 +18606,13 @@
         <v>189</v>
       </c>
       <c r="AN99" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>27</v>
       </c>
-      <c r="AO99" s="16"/>
+      <c r="AO99" s="16">
+        <f t="shared" si="29"/>
+        <v>26.31111111111111</v>
+      </c>
       <c r="AP99" s="16"/>
       <c r="AQ99" s="16"/>
       <c r="AR99" s="16"/>
@@ -18382,11 +18653,11 @@
         <v>128</v>
       </c>
       <c r="L100" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-12</v>
       </c>
       <c r="M100" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>116</v>
       </c>
       <c r="N100" s="16"/>
@@ -18405,26 +18676,26 @@
       <c r="W100" s="16"/>
       <c r="X100" s="16"/>
       <c r="Y100" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>23.2</v>
       </c>
       <c r="Z100" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>21.299999999999955</v>
       </c>
       <c r="AA100" s="4">
         <v>320</v>
       </c>
-      <c r="AB100" s="24" t="str">
+      <c r="AB100" s="16" t="str">
         <f>VLOOKUP(A100,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC100" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>23.875000000000004</v>
       </c>
       <c r="AD100" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>10.081896551724141</v>
       </c>
       <c r="AE100" s="16">
@@ -18455,10 +18726,13 @@
         <v>189</v>
       </c>
       <c r="AN100" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>22</v>
       </c>
-      <c r="AO100" s="16"/>
+      <c r="AO100" s="16">
+        <f t="shared" si="29"/>
+        <v>21.977777777777774</v>
+      </c>
       <c r="AP100" s="16"/>
       <c r="AQ100" s="16"/>
       <c r="AR100" s="16"/>
@@ -18499,11 +18773,11 @@
         <v>122</v>
       </c>
       <c r="L101" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-45</v>
       </c>
       <c r="M101" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>77</v>
       </c>
       <c r="N101" s="10"/>
@@ -18522,26 +18796,26 @@
       <c r="W101" s="10"/>
       <c r="X101" s="10"/>
       <c r="Y101" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15.4</v>
       </c>
       <c r="Z101" s="12">
         <v>0</v>
       </c>
       <c r="AA101" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB101" s="26" t="str">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB101" s="25" t="str">
         <f>VLOOKUP(A101,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC101" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.38961038961038963</v>
       </c>
       <c r="AD101" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.38961038961038963</v>
       </c>
       <c r="AE101" s="10">
@@ -18570,10 +18844,13 @@
       </c>
       <c r="AM101" s="10"/>
       <c r="AN101" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO101" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO101" s="16">
+        <f t="shared" si="29"/>
+        <v>14.799999999999999</v>
+      </c>
       <c r="AP101" s="16"/>
       <c r="AQ101" s="16"/>
       <c r="AR101" s="16"/>
@@ -18612,11 +18889,11 @@
         <v>27</v>
       </c>
       <c r="L102" s="16">
-        <f t="shared" ref="L102:L133" si="31">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="33">E102-K102</f>
         <v>-5</v>
       </c>
       <c r="M102" s="16">
-        <f t="shared" ref="M102:M133" si="32">E102-N102</f>
+        <f t="shared" ref="M102:M133" si="34">E102-N102</f>
         <v>22</v>
       </c>
       <c r="N102" s="16"/>
@@ -18635,7 +18912,7 @@
       <c r="W102" s="16"/>
       <c r="X102" s="16"/>
       <c r="Y102" s="16">
-        <f t="shared" ref="Y102:Y134" si="33">M102/5</f>
+        <f t="shared" ref="Y102:Y134" si="35">M102/5</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="Z102" s="4">
@@ -18643,16 +18920,16 @@
         <v>27.200000000000003</v>
       </c>
       <c r="AA102" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>27.200000000000003</v>
       </c>
-      <c r="AB102" s="24"/>
+      <c r="AB102" s="16"/>
       <c r="AC102" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8</v>
       </c>
       <c r="AD102" s="16">
-        <f t="shared" ref="AD102:AD134" si="34">(F102+O102+P102+Q102+R102+S102+T102+U102+V102+W102+X102)/Y102</f>
+        <f t="shared" ref="AD102:AD134" si="36">(F102+O102+P102+Q102+R102+S102+T102+U102+V102+W102+X102)/Y102</f>
         <v>1.8181818181818181</v>
       </c>
       <c r="AE102" s="16">
@@ -18681,10 +18958,13 @@
       </c>
       <c r="AM102" s="16"/>
       <c r="AN102" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
-      <c r="AO102" s="16"/>
+      <c r="AO102" s="16">
+        <f t="shared" si="29"/>
+        <v>2.6222222222222222</v>
+      </c>
       <c r="AP102" s="16"/>
       <c r="AQ102" s="16"/>
       <c r="AR102" s="16"/>
@@ -18725,11 +19005,11 @@
         <v>10.6</v>
       </c>
       <c r="L103" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.34400000000000119</v>
       </c>
       <c r="M103" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10.944000000000001</v>
       </c>
       <c r="N103" s="16"/>
@@ -18748,21 +19028,21 @@
       <c r="W103" s="16"/>
       <c r="X103" s="16"/>
       <c r="Y103" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>2.1888000000000001</v>
       </c>
       <c r="Z103" s="4"/>
       <c r="AA103" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB103" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB103" s="16"/>
       <c r="AC103" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17.832739400584799</v>
       </c>
       <c r="AD103" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>17.832739400584799</v>
       </c>
       <c r="AE103" s="16">
@@ -18791,10 +19071,13 @@
       </c>
       <c r="AM103" s="16"/>
       <c r="AN103" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO103" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO103" s="16">
+        <f t="shared" si="29"/>
+        <v>2.5809777777777771</v>
+      </c>
       <c r="AP103" s="16"/>
       <c r="AQ103" s="16"/>
       <c r="AR103" s="16"/>
@@ -18833,11 +19116,11 @@
         <v>132</v>
       </c>
       <c r="L104" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-132</v>
       </c>
       <c r="M104" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N104" s="16"/>
@@ -18856,26 +19139,26 @@
       <c r="W104" s="16"/>
       <c r="X104" s="16"/>
       <c r="Y104" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z104" s="4">
-        <f t="shared" ref="Z104" si="35">11*Y104-X104-W104-V104-U104-T104-S104-R104-Q104-P104-O104-F104</f>
+        <f t="shared" ref="Z104" si="37">11*Y104-X104-W104-V104-U104-T104-S104-R104-Q104-P104-O104-F104</f>
         <v>13</v>
       </c>
       <c r="AA104" s="4">
         <v>315</v>
       </c>
-      <c r="AB104" s="24" t="str">
+      <c r="AB104" s="16" t="str">
         <f>VLOOKUP(A104,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC104" s="16" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD104" s="16" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE104" s="16">
@@ -18906,10 +19189,13 @@
         <v>189</v>
       </c>
       <c r="AN104" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>35</v>
       </c>
-      <c r="AO104" s="16"/>
+      <c r="AO104" s="16">
+        <f t="shared" si="29"/>
+        <v>1.2666666666666666</v>
+      </c>
       <c r="AP104" s="16"/>
       <c r="AQ104" s="16"/>
       <c r="AR104" s="16"/>
@@ -18938,11 +19224,11 @@
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
       <c r="L105" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M105" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N105" s="10"/>
@@ -18961,21 +19247,21 @@
       <c r="W105" s="10"/>
       <c r="X105" s="10"/>
       <c r="Y105" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z105" s="12"/>
       <c r="AA105" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB105" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB105" s="16"/>
       <c r="AC105" s="16" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD105" s="10" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE105" s="10">
@@ -19006,10 +19292,13 @@
         <v>64</v>
       </c>
       <c r="AN105" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO105" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO105" s="16">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AP105" s="16"/>
       <c r="AQ105" s="16"/>
       <c r="AR105" s="16"/>
@@ -19050,11 +19339,11 @@
         <v>276</v>
       </c>
       <c r="L106" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-44</v>
       </c>
       <c r="M106" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>232</v>
       </c>
       <c r="N106" s="16"/>
@@ -19075,23 +19364,23 @@
       <c r="W106" s="16"/>
       <c r="X106" s="16"/>
       <c r="Y106" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>46.4</v>
       </c>
       <c r="Z106" s="4"/>
       <c r="AA106" s="4">
         <v>300</v>
       </c>
-      <c r="AB106" s="24" t="str">
+      <c r="AB106" s="16" t="str">
         <f>VLOOKUP(A106,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC106" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19.407327586206897</v>
       </c>
       <c r="AD106" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>12.941810344827587</v>
       </c>
       <c r="AE106" s="16">
@@ -19122,10 +19411,13 @@
         <v>189</v>
       </c>
       <c r="AN106" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>24</v>
       </c>
-      <c r="AO106" s="16"/>
+      <c r="AO106" s="16">
+        <f t="shared" si="29"/>
+        <v>46.511111111111106</v>
+      </c>
       <c r="AP106" s="16"/>
       <c r="AQ106" s="16"/>
       <c r="AR106" s="16"/>
@@ -19166,11 +19458,11 @@
         <v>259</v>
       </c>
       <c r="L107" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-130</v>
       </c>
       <c r="M107" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>129</v>
       </c>
       <c r="N107" s="16"/>
@@ -19189,26 +19481,26 @@
       <c r="W107" s="16"/>
       <c r="X107" s="16"/>
       <c r="Y107" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>25.8</v>
       </c>
       <c r="Z107" s="4">
-        <f t="shared" ref="Z107:Z117" si="36">11*Y107-X107-W107-V107-U107-T107-S107-R107-Q107-P107-O107-F107</f>
+        <f t="shared" ref="Z107:Z117" si="38">11*Y107-X107-W107-V107-U107-T107-S107-R107-Q107-P107-O107-F107</f>
         <v>106</v>
       </c>
       <c r="AA107" s="4">
         <v>400</v>
       </c>
-      <c r="AB107" s="24" t="str">
+      <c r="AB107" s="16" t="str">
         <f>VLOOKUP(A107,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC107" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>22.395348837209301</v>
       </c>
       <c r="AD107" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>6.8914728682170541</v>
       </c>
       <c r="AE107" s="16">
@@ -19239,10 +19531,13 @@
         <v>189</v>
       </c>
       <c r="AN107" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>32</v>
       </c>
-      <c r="AO107" s="16"/>
+      <c r="AO107" s="16">
+        <f t="shared" si="29"/>
+        <v>24.088888888888892</v>
+      </c>
       <c r="AP107" s="16"/>
       <c r="AQ107" s="16"/>
       <c r="AR107" s="16"/>
@@ -19283,11 +19578,11 @@
         <v>103</v>
       </c>
       <c r="L108" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-49</v>
       </c>
       <c r="M108" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>54</v>
       </c>
       <c r="N108" s="16"/>
@@ -19306,23 +19601,23 @@
       <c r="W108" s="16"/>
       <c r="X108" s="16"/>
       <c r="Y108" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>10.8</v>
       </c>
       <c r="Z108" s="4"/>
       <c r="AA108" s="4">
         <v>300</v>
       </c>
-      <c r="AB108" s="24" t="str">
+      <c r="AB108" s="16" t="str">
         <f>VLOOKUP(A108,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC108" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>43.296296296296298</v>
       </c>
       <c r="AD108" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>15.518518518518517</v>
       </c>
       <c r="AE108" s="16">
@@ -19353,10 +19648,13 @@
         <v>189</v>
       </c>
       <c r="AN108" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>51</v>
       </c>
-      <c r="AO108" s="16"/>
+      <c r="AO108" s="16">
+        <f t="shared" si="29"/>
+        <v>8.1777777777777789</v>
+      </c>
       <c r="AP108" s="16"/>
       <c r="AQ108" s="16"/>
       <c r="AR108" s="16"/>
@@ -19397,11 +19695,11 @@
         <v>198.2</v>
       </c>
       <c r="L109" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-3.1809999999999832</v>
       </c>
       <c r="M109" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>195.01900000000001</v>
       </c>
       <c r="N109" s="16"/>
@@ -19420,21 +19718,21 @@
       <c r="W109" s="16"/>
       <c r="X109" s="16"/>
       <c r="Y109" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>39.003799999999998</v>
       </c>
       <c r="Z109" s="4"/>
       <c r="AA109" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB109" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB109" s="16"/>
       <c r="AC109" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.330113988893391</v>
       </c>
       <c r="AD109" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>11.330113988893391</v>
       </c>
       <c r="AE109" s="16">
@@ -19463,10 +19761,13 @@
       </c>
       <c r="AM109" s="16"/>
       <c r="AN109" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO109" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO109" s="16">
+        <f t="shared" si="29"/>
+        <v>46.08153333333334</v>
+      </c>
       <c r="AP109" s="16"/>
       <c r="AQ109" s="16"/>
       <c r="AR109" s="16"/>
@@ -19507,11 +19808,11 @@
         <v>82</v>
       </c>
       <c r="L110" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-10.923000000000002</v>
       </c>
       <c r="M110" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>71.076999999999998</v>
       </c>
       <c r="N110" s="16"/>
@@ -19530,21 +19831,21 @@
       <c r="W110" s="16"/>
       <c r="X110" s="16"/>
       <c r="Y110" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>14.215399999999999</v>
       </c>
       <c r="Z110" s="4"/>
       <c r="AA110" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB110" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB110" s="16"/>
       <c r="AC110" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16.088256397990914</v>
       </c>
       <c r="AD110" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>16.088256397990914</v>
       </c>
       <c r="AE110" s="16">
@@ -19573,10 +19874,13 @@
       </c>
       <c r="AM110" s="16"/>
       <c r="AN110" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO110" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO110" s="16">
+        <f t="shared" si="29"/>
+        <v>12.808800000000002</v>
+      </c>
       <c r="AP110" s="16"/>
       <c r="AQ110" s="16"/>
       <c r="AR110" s="16"/>
@@ -19617,11 +19921,11 @@
         <v>183.1</v>
       </c>
       <c r="L111" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-3.1730000000000018</v>
       </c>
       <c r="M111" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>179.92699999999999</v>
       </c>
       <c r="N111" s="16"/>
@@ -19642,21 +19946,21 @@
       <c r="W111" s="16"/>
       <c r="X111" s="16"/>
       <c r="Y111" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>35.985399999999998</v>
       </c>
       <c r="Z111" s="4"/>
       <c r="AA111" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB111" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB111" s="16"/>
       <c r="AC111" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.440734297798551</v>
       </c>
       <c r="AD111" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>11.440734297798551</v>
       </c>
       <c r="AE111" s="16">
@@ -19685,10 +19989,13 @@
       </c>
       <c r="AM111" s="16"/>
       <c r="AN111" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO111" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO111" s="16">
+        <f t="shared" si="29"/>
+        <v>36.041111111111114</v>
+      </c>
       <c r="AP111" s="16"/>
       <c r="AQ111" s="16"/>
       <c r="AR111" s="16"/>
@@ -19727,11 +20034,11 @@
         <v>49</v>
       </c>
       <c r="L112" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-12</v>
       </c>
       <c r="M112" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>37</v>
       </c>
       <c r="N112" s="16"/>
@@ -19750,21 +20057,21 @@
       <c r="W112" s="16"/>
       <c r="X112" s="16"/>
       <c r="Y112" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7.4</v>
       </c>
       <c r="Z112" s="4"/>
       <c r="AA112" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB112" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB112" s="16"/>
       <c r="AC112" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10.554054054054053</v>
       </c>
       <c r="AD112" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10.554054054054053</v>
       </c>
       <c r="AE112" s="16">
@@ -19793,10 +20100,13 @@
       </c>
       <c r="AM112" s="16"/>
       <c r="AN112" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO112" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO112" s="16">
+        <f t="shared" si="29"/>
+        <v>8.0444444444444443</v>
+      </c>
       <c r="AP112" s="16"/>
       <c r="AQ112" s="16"/>
       <c r="AR112" s="16"/>
@@ -19835,11 +20145,11 @@
         <v>4.0659999999999998</v>
       </c>
       <c r="L113" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="M113" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>4.1459999999999999</v>
       </c>
       <c r="N113" s="16"/>
@@ -19858,23 +20168,23 @@
       <c r="W113" s="16"/>
       <c r="X113" s="16"/>
       <c r="Y113" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.82919999999999994</v>
       </c>
       <c r="Z113" s="4">
         <v>4</v>
       </c>
       <c r="AA113" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="AB113" s="24"/>
+      <c r="AB113" s="16"/>
       <c r="AC113" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14.153883260974434</v>
       </c>
       <c r="AD113" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>9.3299565846599144</v>
       </c>
       <c r="AE113" s="16">
@@ -19903,10 +20213,13 @@
       </c>
       <c r="AM113" s="16"/>
       <c r="AN113" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AO113" s="16"/>
+      <c r="AO113" s="16">
+        <f t="shared" si="29"/>
+        <v>0.50380000000000003</v>
+      </c>
       <c r="AP113" s="16"/>
       <c r="AQ113" s="16"/>
       <c r="AR113" s="16"/>
@@ -19947,11 +20260,11 @@
         <v>366</v>
       </c>
       <c r="L114" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-75</v>
       </c>
       <c r="M114" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>291</v>
       </c>
       <c r="N114" s="16"/>
@@ -19970,24 +20283,24 @@
       <c r="W114" s="16"/>
       <c r="X114" s="16"/>
       <c r="Y114" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>58.2</v>
       </c>
       <c r="Z114" s="4">
+        <f t="shared" si="38"/>
+        <v>75.004000000000019</v>
+      </c>
+      <c r="AA114" s="4">
+        <f t="shared" si="26"/>
+        <v>75.004000000000019</v>
+      </c>
+      <c r="AB114" s="16"/>
+      <c r="AC114" s="16">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="AD114" s="16">
         <f t="shared" si="36"/>
-        <v>75.004000000000019</v>
-      </c>
-      <c r="AA114" s="4">
-        <f t="shared" si="25"/>
-        <v>75.004000000000019</v>
-      </c>
-      <c r="AB114" s="24"/>
-      <c r="AC114" s="16">
-        <f t="shared" si="26"/>
-        <v>11</v>
-      </c>
-      <c r="AD114" s="16">
-        <f t="shared" si="34"/>
         <v>9.7112714776632298</v>
       </c>
       <c r="AE114" s="16">
@@ -20016,10 +20329,13 @@
       </c>
       <c r="AM114" s="16"/>
       <c r="AN114" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>21</v>
       </c>
-      <c r="AO114" s="16"/>
+      <c r="AO114" s="16">
+        <f t="shared" si="29"/>
+        <v>69.977777777777789</v>
+      </c>
       <c r="AP114" s="16"/>
       <c r="AQ114" s="16"/>
       <c r="AR114" s="16"/>
@@ -20060,11 +20376,11 @@
         <v>387</v>
       </c>
       <c r="L115" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-69</v>
       </c>
       <c r="M115" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>318</v>
       </c>
       <c r="N115" s="16"/>
@@ -20087,21 +20403,21 @@
       </c>
       <c r="X115" s="16"/>
       <c r="Y115" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>63.6</v>
       </c>
       <c r="Z115" s="4"/>
       <c r="AA115" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB115" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB115" s="16"/>
       <c r="AC115" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17.083156150943395</v>
       </c>
       <c r="AD115" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>17.083156150943395</v>
       </c>
       <c r="AE115" s="16">
@@ -20130,10 +20446,13 @@
       </c>
       <c r="AM115" s="16"/>
       <c r="AN115" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO115" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO115" s="16">
+        <f t="shared" si="29"/>
+        <v>61.818266666666673</v>
+      </c>
       <c r="AP115" s="16"/>
       <c r="AQ115" s="16"/>
       <c r="AR115" s="16"/>
@@ -20174,11 +20493,11 @@
         <v>507</v>
       </c>
       <c r="L116" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-29</v>
       </c>
       <c r="M116" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>478</v>
       </c>
       <c r="N116" s="16"/>
@@ -20199,21 +20518,21 @@
       <c r="W116" s="16"/>
       <c r="X116" s="16"/>
       <c r="Y116" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>95.6</v>
       </c>
       <c r="Z116" s="4"/>
       <c r="AA116" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB116" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB116" s="16"/>
       <c r="AC116" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14.134644351464436</v>
       </c>
       <c r="AD116" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>14.134644351464436</v>
       </c>
       <c r="AE116" s="16">
@@ -20242,10 +20561,13 @@
       </c>
       <c r="AM116" s="16"/>
       <c r="AN116" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO116" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO116" s="16">
+        <f t="shared" si="29"/>
+        <v>100.45555555555555</v>
+      </c>
       <c r="AP116" s="16"/>
       <c r="AQ116" s="16"/>
       <c r="AR116" s="16"/>
@@ -20286,11 +20608,11 @@
         <v>94</v>
       </c>
       <c r="L117" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-23</v>
       </c>
       <c r="M117" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>71</v>
       </c>
       <c r="N117" s="16"/>
@@ -20309,24 +20631,24 @@
       <c r="W117" s="16"/>
       <c r="X117" s="16"/>
       <c r="Y117" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>14.2</v>
       </c>
       <c r="Z117" s="4">
+        <f t="shared" si="38"/>
+        <v>52.02000000000001</v>
+      </c>
+      <c r="AA117" s="4">
+        <f t="shared" si="26"/>
+        <v>52.02000000000001</v>
+      </c>
+      <c r="AB117" s="16"/>
+      <c r="AC117" s="16">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="AD117" s="16">
         <f t="shared" si="36"/>
-        <v>52.02000000000001</v>
-      </c>
-      <c r="AA117" s="4">
-        <f t="shared" si="25"/>
-        <v>52.02000000000001</v>
-      </c>
-      <c r="AB117" s="24"/>
-      <c r="AC117" s="16">
-        <f t="shared" si="26"/>
-        <v>11</v>
-      </c>
-      <c r="AD117" s="16">
-        <f t="shared" si="34"/>
         <v>7.3366197183098576</v>
       </c>
       <c r="AE117" s="16">
@@ -20355,10 +20677,13 @@
       </c>
       <c r="AM117" s="16"/>
       <c r="AN117" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="AO117" s="16"/>
+      <c r="AO117" s="16">
+        <f t="shared" si="29"/>
+        <v>9.6888888888888882</v>
+      </c>
       <c r="AP117" s="16"/>
       <c r="AQ117" s="16"/>
       <c r="AR117" s="16"/>
@@ -20397,11 +20722,11 @@
         <v>6.6</v>
       </c>
       <c r="L118" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.15600000000000058</v>
       </c>
       <c r="M118" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>6.7560000000000002</v>
       </c>
       <c r="N118" s="10"/>
@@ -20420,21 +20745,21 @@
       <c r="W118" s="10"/>
       <c r="X118" s="10"/>
       <c r="Y118" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1.3512</v>
       </c>
       <c r="Z118" s="12"/>
       <c r="AA118" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB118" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB118" s="16"/>
       <c r="AC118" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>39.911190053285971</v>
       </c>
       <c r="AD118" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>39.911190053285971</v>
       </c>
       <c r="AE118" s="10">
@@ -20465,10 +20790,13 @@
         <v>136</v>
       </c>
       <c r="AN118" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO118" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO118" s="16">
+        <f t="shared" si="29"/>
+        <v>1.5043777777777778</v>
+      </c>
       <c r="AP118" s="16"/>
       <c r="AQ118" s="16"/>
       <c r="AR118" s="16"/>
@@ -20507,11 +20835,11 @@
         <v>52.5</v>
       </c>
       <c r="L119" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-1.142000000000003</v>
       </c>
       <c r="M119" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>51.357999999999997</v>
       </c>
       <c r="N119" s="16"/>
@@ -20530,21 +20858,21 @@
       <c r="W119" s="16"/>
       <c r="X119" s="16"/>
       <c r="Y119" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>10.271599999999999</v>
       </c>
       <c r="Z119" s="4"/>
       <c r="AA119" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB119" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB119" s="16"/>
       <c r="AC119" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16.29531913236497</v>
       </c>
       <c r="AD119" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>16.29531913236497</v>
       </c>
       <c r="AE119" s="16">
@@ -20573,10 +20901,13 @@
       </c>
       <c r="AM119" s="16"/>
       <c r="AN119" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO119" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO119" s="16">
+        <f t="shared" si="29"/>
+        <v>10.506466666666666</v>
+      </c>
       <c r="AP119" s="16"/>
       <c r="AQ119" s="16"/>
       <c r="AR119" s="16"/>
@@ -20617,11 +20948,11 @@
         <v>15</v>
       </c>
       <c r="L120" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-0.39499999999999957</v>
       </c>
       <c r="M120" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>14.605</v>
       </c>
       <c r="N120" s="16"/>
@@ -20640,21 +20971,21 @@
       <c r="W120" s="16"/>
       <c r="X120" s="16"/>
       <c r="Y120" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>2.9210000000000003</v>
       </c>
       <c r="Z120" s="4"/>
       <c r="AA120" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB120" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB120" s="16"/>
       <c r="AC120" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19.622389592605273</v>
       </c>
       <c r="AD120" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>19.622389592605273</v>
       </c>
       <c r="AE120" s="16">
@@ -20683,10 +21014,13 @@
       </c>
       <c r="AM120" s="16"/>
       <c r="AN120" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO120" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO120" s="16">
+        <f t="shared" si="29"/>
+        <v>6.1193999999999997</v>
+      </c>
       <c r="AP120" s="16"/>
       <c r="AQ120" s="16"/>
       <c r="AR120" s="16"/>
@@ -20727,11 +21061,11 @@
         <v>79</v>
       </c>
       <c r="L121" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-7</v>
       </c>
       <c r="M121" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>72</v>
       </c>
       <c r="N121" s="16"/>
@@ -20750,26 +21084,26 @@
       <c r="W121" s="16"/>
       <c r="X121" s="16"/>
       <c r="Y121" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>14.4</v>
       </c>
       <c r="Z121" s="4">
-        <f t="shared" ref="Z121:Z131" si="37">11*Y121-X121-W121-V121-U121-T121-S121-R121-Q121-P121-O121-F121</f>
+        <f t="shared" ref="Z121:Z131" si="39">11*Y121-X121-W121-V121-U121-T121-S121-R121-Q121-P121-O121-F121</f>
         <v>59.200000000000017</v>
       </c>
       <c r="AA121" s="4">
         <v>360</v>
       </c>
-      <c r="AB121" s="24" t="str">
+      <c r="AB121" s="16" t="str">
         <f>VLOOKUP(A121,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC121" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>31.888888888888886</v>
       </c>
       <c r="AD121" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>6.8888888888888875</v>
       </c>
       <c r="AE121" s="16">
@@ -20800,10 +21134,13 @@
         <v>189</v>
       </c>
       <c r="AN121" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>32</v>
       </c>
-      <c r="AO121" s="16"/>
+      <c r="AO121" s="16">
+        <f t="shared" si="29"/>
+        <v>9.2666666666666675</v>
+      </c>
       <c r="AP121" s="16"/>
       <c r="AQ121" s="16"/>
       <c r="AR121" s="16"/>
@@ -20844,11 +21181,11 @@
         <v>62</v>
       </c>
       <c r="L122" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-17</v>
       </c>
       <c r="M122" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>45</v>
       </c>
       <c r="N122" s="16"/>
@@ -20867,23 +21204,23 @@
       <c r="W122" s="16"/>
       <c r="X122" s="16"/>
       <c r="Y122" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="Z122" s="4"/>
       <c r="AA122" s="4">
         <v>300</v>
       </c>
-      <c r="AB122" s="24" t="str">
+      <c r="AB122" s="16" t="str">
         <f>VLOOKUP(A122,[1]Sheet!$A:$AA,27,0)</f>
         <v xml:space="preserve">300 увеличить сеть Молоко </v>
       </c>
       <c r="AC122" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>48.488888888888887</v>
       </c>
       <c r="AD122" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>15.155555555555557</v>
       </c>
       <c r="AE122" s="16">
@@ -20914,10 +21251,13 @@
         <v>189</v>
       </c>
       <c r="AN122" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>27</v>
       </c>
-      <c r="AO122" s="16"/>
+      <c r="AO122" s="16">
+        <f t="shared" si="29"/>
+        <v>7.0888888888888886</v>
+      </c>
       <c r="AP122" s="16"/>
       <c r="AQ122" s="16"/>
       <c r="AR122" s="16"/>
@@ -20958,11 +21298,11 @@
         <v>30.332999999999998</v>
       </c>
       <c r="L123" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>4.1559999999999988</v>
       </c>
       <c r="M123" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>34.488999999999997</v>
       </c>
       <c r="N123" s="16"/>
@@ -20981,21 +21321,21 @@
       <c r="W123" s="16"/>
       <c r="X123" s="16"/>
       <c r="Y123" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6.8977999999999993</v>
       </c>
       <c r="Z123" s="4"/>
       <c r="AA123" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB123" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB123" s="16"/>
       <c r="AC123" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21.084171764910565</v>
       </c>
       <c r="AD123" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>21.084171764910565</v>
       </c>
       <c r="AE123" s="16">
@@ -21026,10 +21366,13 @@
         <v>173</v>
       </c>
       <c r="AN123" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO123" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO123" s="16">
+        <f t="shared" si="29"/>
+        <v>10.300622222222222</v>
+      </c>
       <c r="AP123" s="16"/>
       <c r="AQ123" s="16"/>
       <c r="AR123" s="16"/>
@@ -21070,11 +21413,11 @@
         <v>482.084</v>
       </c>
       <c r="L124" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-18.66500000000002</v>
       </c>
       <c r="M124" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>463.41899999999998</v>
       </c>
       <c r="N124" s="16"/>
@@ -21095,21 +21438,21 @@
       <c r="W124" s="16"/>
       <c r="X124" s="16"/>
       <c r="Y124" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>92.683799999999991</v>
       </c>
       <c r="Z124" s="4"/>
       <c r="AA124" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB124" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB124" s="16"/>
       <c r="AC124" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13.994017530571687</v>
       </c>
       <c r="AD124" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>13.994017530571687</v>
       </c>
       <c r="AE124" s="16">
@@ -21138,10 +21481,13 @@
       </c>
       <c r="AM124" s="16"/>
       <c r="AN124" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO124" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO124" s="16">
+        <f t="shared" si="29"/>
+        <v>103.56319999999999</v>
+      </c>
       <c r="AP124" s="16"/>
       <c r="AQ124" s="16"/>
       <c r="AR124" s="16"/>
@@ -21182,11 +21528,11 @@
         <v>58.6</v>
       </c>
       <c r="L125" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-11.505000000000003</v>
       </c>
       <c r="M125" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>47.094999999999999</v>
       </c>
       <c r="N125" s="16"/>
@@ -21205,21 +21551,21 @@
       <c r="W125" s="16"/>
       <c r="X125" s="16"/>
       <c r="Y125" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9.4190000000000005</v>
       </c>
       <c r="Z125" s="4"/>
       <c r="AA125" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB125" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB125" s="16"/>
       <c r="AC125" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>31.627773649007324</v>
       </c>
       <c r="AD125" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>31.627773649007324</v>
       </c>
       <c r="AE125" s="16">
@@ -21250,10 +21596,13 @@
         <v>185</v>
       </c>
       <c r="AN125" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO125" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO125" s="16">
+        <f t="shared" si="29"/>
+        <v>9.6058666666666674</v>
+      </c>
       <c r="AP125" s="16"/>
       <c r="AQ125" s="16"/>
       <c r="AR125" s="16"/>
@@ -21295,11 +21644,11 @@
         <v>1026.5</v>
       </c>
       <c r="L126" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-44.303999999999974</v>
       </c>
       <c r="M126" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>982.19600000000003</v>
       </c>
       <c r="N126" s="16"/>
@@ -21322,21 +21671,21 @@
       <c r="W126" s="16"/>
       <c r="X126" s="16"/>
       <c r="Y126" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>196.4392</v>
       </c>
       <c r="Z126" s="4"/>
       <c r="AA126" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB126" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB126" s="16"/>
       <c r="AC126" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17.154712501374469</v>
       </c>
       <c r="AD126" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>17.154712501374469</v>
       </c>
       <c r="AE126" s="16">
@@ -21365,10 +21714,13 @@
       </c>
       <c r="AM126" s="16"/>
       <c r="AN126" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO126" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO126" s="16">
+        <f t="shared" si="29"/>
+        <v>160.73188888888888</v>
+      </c>
       <c r="AP126" s="16"/>
       <c r="AQ126" s="16"/>
       <c r="AR126" s="16"/>
@@ -21405,11 +21757,11 @@
         <v>82</v>
       </c>
       <c r="L127" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-1</v>
       </c>
       <c r="M127" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>81</v>
       </c>
       <c r="N127" s="16"/>
@@ -21428,24 +21780,24 @@
       <c r="W127" s="16"/>
       <c r="X127" s="16"/>
       <c r="Y127" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>16.2</v>
       </c>
       <c r="Z127" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>55.199999999999989</v>
       </c>
       <c r="AA127" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>55.199999999999989</v>
       </c>
-      <c r="AB127" s="24"/>
+      <c r="AB127" s="16"/>
       <c r="AC127" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11</v>
       </c>
       <c r="AD127" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>7.5925925925925926</v>
       </c>
       <c r="AE127" s="16">
@@ -21476,10 +21828,13 @@
         <v>177</v>
       </c>
       <c r="AN127" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>14</v>
       </c>
-      <c r="AO127" s="16"/>
+      <c r="AO127" s="16">
+        <f t="shared" si="29"/>
+        <v>1.7999999999999998</v>
+      </c>
       <c r="AP127" s="16"/>
       <c r="AQ127" s="16"/>
       <c r="AR127" s="16"/>
@@ -21516,11 +21871,11 @@
         <v>49</v>
       </c>
       <c r="L128" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M128" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>49</v>
       </c>
       <c r="N128" s="16"/>
@@ -21539,21 +21894,21 @@
       <c r="W128" s="16"/>
       <c r="X128" s="16"/>
       <c r="Y128" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="Z128" s="4"/>
       <c r="AA128" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB128" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB128" s="16"/>
       <c r="AC128" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15.816326530612244</v>
       </c>
       <c r="AD128" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>15.816326530612244</v>
       </c>
       <c r="AE128" s="16">
@@ -21584,10 +21939,13 @@
         <v>177</v>
       </c>
       <c r="AN128" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO128" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO128" s="16">
+        <f t="shared" si="29"/>
+        <v>1.088888888888889</v>
+      </c>
       <c r="AP128" s="16"/>
       <c r="AQ128" s="16"/>
       <c r="AR128" s="16"/>
@@ -21624,11 +21982,11 @@
         <v>66</v>
       </c>
       <c r="L129" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M129" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>66</v>
       </c>
       <c r="N129" s="16"/>
@@ -21647,24 +22005,24 @@
       <c r="W129" s="16"/>
       <c r="X129" s="16"/>
       <c r="Y129" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>13.2</v>
       </c>
       <c r="Z129" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>7.1999999999999886</v>
       </c>
       <c r="AA129" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.1999999999999886</v>
       </c>
-      <c r="AB129" s="24"/>
+      <c r="AB129" s="16"/>
       <c r="AC129" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11</v>
       </c>
       <c r="AD129" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10.454545454545455</v>
       </c>
       <c r="AE129" s="16">
@@ -21695,10 +22053,13 @@
         <v>177</v>
       </c>
       <c r="AN129" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2</v>
       </c>
-      <c r="AO129" s="16"/>
+      <c r="AO129" s="16">
+        <f t="shared" si="29"/>
+        <v>1.4666666666666666</v>
+      </c>
       <c r="AP129" s="16"/>
       <c r="AQ129" s="16"/>
       <c r="AR129" s="16"/>
@@ -21739,11 +22100,11 @@
         <v>191</v>
       </c>
       <c r="L130" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-96</v>
       </c>
       <c r="M130" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>95</v>
       </c>
       <c r="N130" s="16"/>
@@ -21762,21 +22123,21 @@
       <c r="W130" s="16"/>
       <c r="X130" s="16"/>
       <c r="Y130" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>19</v>
       </c>
       <c r="Z130" s="4"/>
       <c r="AA130" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB130" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB130" s="16"/>
       <c r="AC130" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19.389473684210529</v>
       </c>
       <c r="AD130" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>19.389473684210529</v>
       </c>
       <c r="AE130" s="16">
@@ -21805,10 +22166,13 @@
       </c>
       <c r="AM130" s="16"/>
       <c r="AN130" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO130" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO130" s="16">
+        <f t="shared" si="29"/>
+        <v>29.777777777777779</v>
+      </c>
       <c r="AP130" s="16"/>
       <c r="AQ130" s="16"/>
       <c r="AR130" s="16"/>
@@ -21849,11 +22213,11 @@
         <v>147</v>
       </c>
       <c r="L131" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-18</v>
       </c>
       <c r="M131" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>129</v>
       </c>
       <c r="N131" s="16"/>
@@ -21872,24 +22236,24 @@
       <c r="W131" s="16"/>
       <c r="X131" s="16"/>
       <c r="Y131" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>25.8</v>
       </c>
       <c r="Z131" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>119.6</v>
       </c>
       <c r="AA131" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>119.6</v>
       </c>
-      <c r="AB131" s="24"/>
+      <c r="AB131" s="16"/>
       <c r="AC131" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11</v>
       </c>
       <c r="AD131" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>6.3643410852713185</v>
       </c>
       <c r="AE131" s="16">
@@ -21918,10 +22282,13 @@
       </c>
       <c r="AM131" s="16"/>
       <c r="AN131" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>36</v>
       </c>
-      <c r="AO131" s="16"/>
+      <c r="AO131" s="16">
+        <f t="shared" si="29"/>
+        <v>23.155555555555555</v>
+      </c>
       <c r="AP131" s="16"/>
       <c r="AQ131" s="16"/>
       <c r="AR131" s="16"/>
@@ -21962,11 +22329,11 @@
         <v>45.75</v>
       </c>
       <c r="L132" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2.8560000000000016</v>
       </c>
       <c r="M132" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>48.606000000000002</v>
       </c>
       <c r="N132" s="16"/>
@@ -21985,21 +22352,21 @@
       <c r="W132" s="16"/>
       <c r="X132" s="16"/>
       <c r="Y132" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9.7211999999999996</v>
       </c>
       <c r="Z132" s="4"/>
       <c r="AA132" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB132" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB132" s="16"/>
       <c r="AC132" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15.854308110109866</v>
       </c>
       <c r="AD132" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>15.854308110109866</v>
       </c>
       <c r="AE132" s="16">
@@ -22028,10 +22395,13 @@
       </c>
       <c r="AM132" s="16"/>
       <c r="AN132" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO132" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO132" s="16">
+        <f t="shared" si="29"/>
+        <v>11.530066666666666</v>
+      </c>
       <c r="AP132" s="16"/>
       <c r="AQ132" s="16"/>
       <c r="AR132" s="16"/>
@@ -22072,11 +22442,11 @@
         <v>67</v>
       </c>
       <c r="L133" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-7</v>
       </c>
       <c r="M133" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>60</v>
       </c>
       <c r="N133" s="16"/>
@@ -22095,23 +22465,23 @@
       <c r="W133" s="16"/>
       <c r="X133" s="16"/>
       <c r="Y133" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>12</v>
       </c>
       <c r="Z133" s="22">
         <v>20</v>
       </c>
       <c r="AA133" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="AB133" s="24"/>
+      <c r="AB133" s="16"/>
       <c r="AC133" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.5</v>
       </c>
       <c r="AD133" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>1.8333333333333333</v>
       </c>
       <c r="AE133" s="16">
@@ -22140,10 +22510,13 @@
       </c>
       <c r="AM133" s="16"/>
       <c r="AN133" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6</v>
       </c>
-      <c r="AO133" s="16"/>
+      <c r="AO133" s="16">
+        <f t="shared" si="29"/>
+        <v>9.844444444444445</v>
+      </c>
       <c r="AP133" s="16"/>
       <c r="AQ133" s="16"/>
       <c r="AR133" s="16"/>
@@ -22184,11 +22557,11 @@
         <v>43</v>
       </c>
       <c r="L134" s="16">
-        <f t="shared" ref="L134" si="38">E134-K134</f>
+        <f t="shared" ref="L134" si="40">E134-K134</f>
         <v>-10</v>
       </c>
       <c r="M134" s="16">
-        <f t="shared" ref="M134" si="39">E134-N134</f>
+        <f t="shared" ref="M134" si="41">E134-N134</f>
         <v>33</v>
       </c>
       <c r="N134" s="16"/>
@@ -22207,21 +22580,21 @@
       <c r="W134" s="16"/>
       <c r="X134" s="16"/>
       <c r="Y134" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6.6</v>
       </c>
       <c r="Z134" s="4"/>
       <c r="AA134" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB134" s="24"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB134" s="16"/>
       <c r="AC134" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15.696969696969697</v>
       </c>
       <c r="AD134" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>15.696969696969697</v>
       </c>
       <c r="AE134" s="16">
@@ -22250,10 +22623,13 @@
       </c>
       <c r="AM134" s="16"/>
       <c r="AN134" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AO134" s="16"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AO134" s="16">
+        <f t="shared" si="29"/>
+        <v>7.2888888888888879</v>
+      </c>
       <c r="AP134" s="16"/>
       <c r="AQ134" s="16"/>
       <c r="AR134" s="16"/>
